--- a/miomio/后台升级表格/到达国仓/执行DPN任务.xlsx
+++ b/miomio/后台升级表格/到达国仓/执行DPN任务.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="12420"/>
+    <workbookView windowHeight="18320"/>
   </bookViews>
   <sheets>
     <sheet name="列表" sheetId="1" r:id="rId1"/>
@@ -15,12 +15,25 @@
     <sheet name="DPN详情 " sheetId="10" r:id="rId6"/>
     <sheet name="点击订单号或更多" sheetId="6" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="182">
   <si>
     <t>全部</t>
   </si>
@@ -176,6 +189,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">JOB123458              </t>
     </r>
     <r>
@@ -191,6 +211,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">190828000021  190828000021  190828000021   190828000021  190828000021  190828000021  190828000021  190828000021  190828000021   190828000021  190828000021  190828000021 </t>
     </r>
     <r>
@@ -214,6 +240,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <charset val="134"/>
+      </rPr>
       <t>已入库</t>
     </r>
     <r>
@@ -234,6 +266,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">JOB123459              </t>
     </r>
     <r>
@@ -249,6 +288,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">JOB123460              </t>
     </r>
     <r>
@@ -264,6 +310,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">JOB123461              </t>
     </r>
     <r>
@@ -279,6 +332,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">JOB123459               </t>
     </r>
     <r>
@@ -346,6 +406,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">JOB123457               </t>
     </r>
     <r>
@@ -367,6 +434,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">JOB123456              </t>
     </r>
     <r>
@@ -385,6 +459,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">JOB123455               </t>
     </r>
     <r>
@@ -403,6 +484,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">JOB123454              </t>
     </r>
     <r>
@@ -421,6 +509,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">JOB123453               </t>
     </r>
     <r>
@@ -439,6 +534,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">JOB123452              </t>
     </r>
     <r>
@@ -457,6 +559,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">JOB123451               </t>
     </r>
     <r>
@@ -475,6 +584,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">JOB123450              </t>
     </r>
     <r>
@@ -493,6 +609,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">JOB123449               </t>
     </r>
     <r>
@@ -511,6 +634,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">JOB123448              </t>
     </r>
     <r>
@@ -529,6 +659,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">JOB123447               </t>
     </r>
     <r>
@@ -547,6 +684,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">JOB123446              </t>
     </r>
     <r>
@@ -565,6 +709,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">JOB123445               </t>
     </r>
     <r>
@@ -583,6 +734,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">JOB123444              </t>
     </r>
     <r>
@@ -601,6 +759,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">JOB123443               </t>
     </r>
     <r>
@@ -619,6 +784,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">JOB123442              </t>
     </r>
     <r>
@@ -637,6 +809,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">JOB123441               </t>
     </r>
     <r>
@@ -664,26 +843,15 @@
   </si>
   <si>
     <r>
-      <t>JOB/</t>
-    </r>
-    <r>
       <rPr>
         <b/>
         <sz val="9"/>
         <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>站点</t>
-    </r>
-  </si>
-  <si>
-    <t>业务员</t>
-  </si>
-  <si>
-    <t>收件人</t>
-  </si>
-  <si>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>JOB/</t>
+    </r>
     <r>
       <rPr>
         <b/>
@@ -692,79 +860,97 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>尺寸</t>
-    </r>
+      <t>站点</t>
+    </r>
+  </si>
+  <si>
+    <t>业务员</t>
+  </si>
+  <si>
+    <t>收件人</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
         <sz val="9"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>CM</t>
-    </r>
-  </si>
-  <si>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>尺寸</t>
+    </r>
     <r>
       <rPr>
         <b/>
         <sz val="9"/>
         <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <charset val="134"/>
-      </rPr>
-      <t>体积</t>
-    </r>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>CM</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
         <sz val="9"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>CBM</t>
-    </r>
-  </si>
-  <si>
+        <rFont val="Microsoft JhengHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>体积</t>
+    </r>
     <r>
       <rPr>
         <b/>
         <sz val="9"/>
         <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <charset val="134"/>
-      </rPr>
-      <t>体积重</t>
-    </r>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>CBM</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
         <sz val="9"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Kg</t>
-    </r>
-  </si>
-  <si>
+        <rFont val="Microsoft JhengHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>体积重</t>
+    </r>
     <r>
       <rPr>
         <b/>
         <sz val="9"/>
         <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <charset val="134"/>
-      </rPr>
-      <t>重量</t>
-    </r>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Kg</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
         <sz val="9"/>
         <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>重量</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
@@ -773,6 +959,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">DPN123456                                IKEJ STA-ABUJ STA             </t>
     </r>
     <r>
@@ -788,6 +981,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">JOB123458                            </t>
     </r>
     <r>
@@ -802,6 +1001,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">191021000022    </t>
     </r>
     <r>
@@ -829,6 +1034,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">JOB123461              </t>
     </r>
     <r>
@@ -843,6 +1054,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">JOB123464                                     </t>
     </r>
     <r>
@@ -857,6 +1074,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">JOB123464                                 </t>
     </r>
     <r>
@@ -908,171 +1131,177 @@
     </r>
   </si>
   <si>
+    <t>电话</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>十</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>8613570217212</t>
+    </r>
+  </si>
+  <si>
+    <t>发往站点</t>
+  </si>
+  <si>
+    <t>ABUJ STA</t>
+  </si>
+  <si>
+    <t>地址</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>广东省广州市白云区黄石路江夏北二路</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>号云商易城</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>栋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>110</t>
+    </r>
+  </si>
+  <si>
+    <t>物流公司</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>选择</t>
+    </r>
+  </si>
+  <si>
+    <t>执行日期</t>
+  </si>
+  <si>
+    <t>选择</t>
+  </si>
+  <si>
+    <t>查询电话</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>录入</t>
+    </r>
+  </si>
+  <si>
+    <t>运输方式</t>
+  </si>
+  <si>
+    <t>空运口    陆运口</t>
+  </si>
+  <si>
+    <t>司机名称</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>录入</t>
+  </si>
+  <si>
+    <t>司机电话</t>
+  </si>
+  <si>
+    <t>车牌</t>
+  </si>
+  <si>
+    <t>返回  发布</t>
+  </si>
+  <si>
     <t>创建日期/账号</t>
   </si>
   <si>
     <t>2019/8/28 15:01:22 CANSAMPAO</t>
   </si>
   <si>
-    <t>电话</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
+    <t>重量</t>
+  </si>
+  <si>
+    <t>500.00KGS</t>
+  </si>
+  <si>
+    <t>运单号/订单号</t>
+  </si>
+  <si>
+    <t>无</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>十</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>8613570217212</t>
-    </r>
-  </si>
-  <si>
-    <t>发往站点</t>
-  </si>
-  <si>
-    <t>ABUJ STA</t>
-  </si>
-  <si>
-    <t>地址</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>广东省广州市白云区黄石路江夏北二路</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>号云商易城</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>B</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>栋</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>110</t>
-    </r>
-  </si>
-  <si>
-    <t>重量</t>
-  </si>
-  <si>
-    <t>500.00KGS</t>
-  </si>
-  <si>
-    <t>物流公司</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>选择</t>
-    </r>
-  </si>
-  <si>
-    <t>运单号/订单号</t>
-  </si>
-  <si>
-    <t>录入</t>
-  </si>
-  <si>
-    <t>执行日期</t>
-  </si>
-  <si>
-    <t>选择</t>
-  </si>
-  <si>
-    <t>查询电话</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>录入</t>
-    </r>
-  </si>
-  <si>
-    <t>运输方式</t>
-  </si>
-  <si>
-    <t>空运口    陆运口</t>
-  </si>
-  <si>
-    <t>司机名称</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>司机电话</t>
-  </si>
-  <si>
-    <t>车牌</t>
-  </si>
-  <si>
-    <t>返回  发布</t>
-  </si>
-  <si>
-    <t>无</t>
-  </si>
-  <si>
-    <r>
       <t>空运</t>
     </r>
     <r>
@@ -1170,14 +1399,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="6">
-    <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="0_ "/>
+    <numFmt numFmtId="176" formatCode="0_ "/>
+    <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
   </numFmts>
   <fonts count="53">
     <font>
@@ -1234,6 +1463,13 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="8"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -1252,13 +1488,6 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1374,23 +1603,9 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1405,7 +1620,62 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1419,31 +1689,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1457,55 +1712,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1518,23 +1733,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Wingdings"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
@@ -1548,8 +1758,27 @@
       <name val="Microsoft JhengHei"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Wingdings"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="41">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1606,7 +1835,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1618,7 +1865,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1630,7 +1901,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1642,103 +1979,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1750,43 +2003,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1820,10 +2043,30 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -1853,94 +2096,9 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
       <top/>
       <bottom style="thin">
         <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1963,8 +2121,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1977,157 +2135,222 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="17" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="29" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="11" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="12" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="12" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="13" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="16" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="16" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="46" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="12" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="46" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="46" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="46" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="46" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="46" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="46" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="46" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="46" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="46" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="46" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="46" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="154">
+  <cellXfs count="140">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2152,19 +2375,25 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2173,229 +2402,190 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="12" fillId="4" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="9" fillId="4" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="12" fillId="5" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="17" fillId="4" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="17" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="177" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="21" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="12" fillId="4" borderId="7" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="22" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="8" fillId="4" borderId="7" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="12" fillId="5" borderId="7" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="17" fillId="4" borderId="7" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="22" fontId="17" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="22" fontId="22" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="22" fontId="22" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="22" fontId="22" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="22" fontId="22" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="10" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="21" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2413,25 +2603,25 @@
     <xf numFmtId="0" fontId="24" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="8" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="11" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -2464,6 +2654,9 @@
     <xf numFmtId="0" fontId="25" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2482,6 +2675,9 @@
     <xf numFmtId="0" fontId="25" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="25" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2497,10 +2693,10 @@
     <xf numFmtId="0" fontId="28" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2509,10 +2705,31 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="1" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2521,71 +2738,35 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="1" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="22" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="22" fontId="1" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="22" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="22" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="22" fontId="1" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="22" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="22" fontId="1" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -2593,52 +2774,52 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -2949,1104 +3130,1104 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:O31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="5.625" style="104" customWidth="1"/>
-    <col min="2" max="2" width="15.625" style="105" customWidth="1"/>
-    <col min="3" max="3" width="20.625" style="104" customWidth="1"/>
-    <col min="4" max="12" width="15.625" style="104" customWidth="1"/>
-    <col min="13" max="13" width="15.625" style="105" customWidth="1"/>
-    <col min="14" max="14" width="15.625" style="104" customWidth="1"/>
-    <col min="15" max="15" width="18.25" style="104" customWidth="1"/>
-    <col min="17" max="18" width="15.625" style="104" customWidth="1"/>
-    <col min="19" max="19" width="13.625" style="104" customWidth="1"/>
-    <col min="20" max="16384" width="9" style="104"/>
+    <col min="1" max="1" width="5.625" style="93" customWidth="1"/>
+    <col min="2" max="2" width="15.625" style="94" customWidth="1"/>
+    <col min="3" max="3" width="20.625" style="93" customWidth="1"/>
+    <col min="4" max="12" width="15.625" style="93" customWidth="1"/>
+    <col min="13" max="13" width="15.625" style="94" customWidth="1"/>
+    <col min="14" max="14" width="15.625" style="93" customWidth="1"/>
+    <col min="15" max="15" width="18.25" style="93" customWidth="1"/>
+    <col min="17" max="18" width="15.625" style="93" customWidth="1"/>
+    <col min="19" max="19" width="13.625" style="93" customWidth="1"/>
+    <col min="20" max="16384" width="9" style="93"/>
   </cols>
   <sheetData>
-    <row r="1" s="102" customFormat="1" ht="30" customHeight="1" spans="1:15">
-      <c r="A1" s="106" t="s">
+    <row r="1" s="91" customFormat="1" ht="30" customHeight="1" spans="1:15">
+      <c r="A1" s="95" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="107" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="108" t="s">
+      <c r="B1" s="96" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="97" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="108" t="s">
+      <c r="D1" s="97" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="109" t="s">
+      <c r="E1" s="98" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="110"/>
-      <c r="G1" s="111"/>
-      <c r="H1" s="111"/>
-      <c r="I1" s="110"/>
-      <c r="J1" s="110"/>
-      <c r="K1" s="110"/>
-      <c r="L1" s="138"/>
-      <c r="M1" s="110"/>
-      <c r="O1" s="110"/>
-    </row>
-    <row r="2" s="102" customFormat="1" ht="30" customHeight="1" spans="1:15">
-      <c r="A2" s="112" t="s">
+      <c r="F1" s="99"/>
+      <c r="G1" s="100"/>
+      <c r="H1" s="100"/>
+      <c r="I1" s="99"/>
+      <c r="J1" s="99"/>
+      <c r="K1" s="99"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="99"/>
+      <c r="O1" s="99"/>
+    </row>
+    <row r="2" s="91" customFormat="1" ht="30" customHeight="1" spans="1:15">
+      <c r="A2" s="102" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="113" t="s">
+      <c r="B2" s="103" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="109" t="s">
+      <c r="C2" s="98" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="109" t="s">
+      <c r="D2" s="98" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="109" t="s">
+      <c r="E2" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="110"/>
-      <c r="G2" s="111"/>
-      <c r="H2" s="111"/>
-      <c r="I2" s="110"/>
-      <c r="J2" s="110"/>
-      <c r="K2" s="110"/>
-      <c r="L2" s="138"/>
-      <c r="M2" s="110"/>
-      <c r="O2" s="110"/>
-    </row>
-    <row r="3" s="102" customFormat="1" ht="30" customHeight="1" spans="1:15">
-      <c r="A3" s="114"/>
-      <c r="B3" s="115"/>
-      <c r="C3" s="114"/>
-      <c r="D3" s="114"/>
-      <c r="E3" s="114"/>
-      <c r="F3" s="114"/>
-      <c r="G3" s="110"/>
-      <c r="H3" s="110"/>
-      <c r="I3" s="110"/>
-      <c r="J3" s="110"/>
-      <c r="K3" s="110"/>
-      <c r="L3" s="138"/>
-      <c r="M3" s="110"/>
-      <c r="O3" s="110"/>
-    </row>
-    <row r="4" s="102" customFormat="1" ht="30" customHeight="1" spans="1:13">
-      <c r="A4" s="116" t="s">
+      <c r="F2" s="99"/>
+      <c r="G2" s="100"/>
+      <c r="H2" s="100"/>
+      <c r="I2" s="99"/>
+      <c r="J2" s="99"/>
+      <c r="K2" s="99"/>
+      <c r="L2" s="101"/>
+      <c r="M2" s="99"/>
+      <c r="O2" s="99"/>
+    </row>
+    <row r="3" s="91" customFormat="1" ht="30" customHeight="1" spans="1:15">
+      <c r="A3" s="104"/>
+      <c r="B3" s="105"/>
+      <c r="C3" s="104"/>
+      <c r="D3" s="104"/>
+      <c r="E3" s="104"/>
+      <c r="F3" s="104"/>
+      <c r="G3" s="99"/>
+      <c r="H3" s="99"/>
+      <c r="I3" s="99"/>
+      <c r="J3" s="99"/>
+      <c r="K3" s="99"/>
+      <c r="L3" s="101"/>
+      <c r="M3" s="99"/>
+      <c r="O3" s="99"/>
+    </row>
+    <row r="4" s="91" customFormat="1" ht="30" customHeight="1" spans="1:15">
+      <c r="A4" s="106" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="117" t="s">
+      <c r="B4" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="106" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="116" t="s">
+      <c r="D4" s="106" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="116" t="s">
+      <c r="E4" s="106" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="116" t="s">
+      <c r="F4" s="106" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="116" t="s">
+      <c r="G4" s="106" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="116" t="s">
+      <c r="H4" s="106" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="116" t="s">
+      <c r="I4" s="106" t="s">
         <v>16</v>
       </c>
-      <c r="J4" s="116" t="s">
+      <c r="J4" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="K4" s="139" t="s">
+      <c r="K4" s="108" t="s">
         <v>18</v>
       </c>
-      <c r="L4" s="116" t="s">
+      <c r="L4" s="106" t="s">
         <v>19</v>
       </c>
-      <c r="M4" s="116" t="s">
+      <c r="M4" s="106" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="5" s="102" customFormat="1" ht="30" customHeight="1" spans="1:13">
-      <c r="A5" s="116" t="s">
+    <row r="5" s="91" customFormat="1" ht="30" customHeight="1" spans="1:15">
+      <c r="A5" s="106" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="117" t="s">
+      <c r="B5" s="107" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="116" t="s">
+      <c r="C5" s="106" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="116" t="s">
+      <c r="D5" s="106" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="116" t="s">
+      <c r="E5" s="106" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="116" t="s">
+      <c r="F5" s="106" t="s">
         <v>25</v>
       </c>
-      <c r="G5" s="116" t="s">
+      <c r="G5" s="106" t="s">
         <v>26</v>
       </c>
-      <c r="H5" s="116" t="s">
+      <c r="H5" s="106" t="s">
         <v>27</v>
       </c>
-      <c r="I5" s="116" t="s">
+      <c r="I5" s="106" t="s">
         <v>28</v>
       </c>
-      <c r="J5" s="116" t="s">
+      <c r="J5" s="106" t="s">
         <v>29</v>
       </c>
-      <c r="K5" s="139" t="s">
+      <c r="K5" s="108" t="s">
         <v>30</v>
       </c>
-      <c r="L5" s="116" t="s">
+      <c r="L5" s="106" t="s">
         <v>31</v>
       </c>
-      <c r="M5" s="116" t="s">
+      <c r="M5" s="106" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="6" s="103" customFormat="1" ht="30" customHeight="1" spans="1:15">
-      <c r="A6" s="118" t="s">
+    <row r="6" s="92" customFormat="1" ht="30" customHeight="1" spans="1:15">
+      <c r="A6" s="109" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="119"/>
-      <c r="C6" s="111" t="s">
+      <c r="B6" s="110"/>
+      <c r="C6" s="100" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="111" t="s">
+      <c r="D6" s="100" t="s">
         <v>35</v>
       </c>
-      <c r="E6" s="111" t="s">
+      <c r="E6" s="100" t="s">
         <v>36</v>
       </c>
-      <c r="F6" s="111" t="s">
+      <c r="F6" s="100" t="s">
         <v>37</v>
       </c>
-      <c r="G6" s="111"/>
-      <c r="H6" s="111"/>
-      <c r="I6" s="111"/>
-      <c r="J6" s="111"/>
-      <c r="K6" s="111"/>
-      <c r="L6" s="119"/>
-      <c r="M6" s="111"/>
-      <c r="O6" s="111"/>
-    </row>
-    <row r="7" s="102" customFormat="1" ht="30" customHeight="1" spans="1:15">
-      <c r="A7" s="120" t="s">
+      <c r="G6" s="100"/>
+      <c r="H6" s="100"/>
+      <c r="I6" s="100"/>
+      <c r="J6" s="100"/>
+      <c r="K6" s="100"/>
+      <c r="L6" s="110"/>
+      <c r="M6" s="100"/>
+      <c r="O6" s="100"/>
+    </row>
+    <row r="7" s="91" customFormat="1" ht="30" customHeight="1" spans="1:15">
+      <c r="A7" s="111" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="121" t="s">
+      <c r="B7" s="112" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="122" t="s">
+      <c r="C7" s="113" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="122" t="s">
+      <c r="D7" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="123" t="s">
+      <c r="E7" s="113" t="s">
         <v>42</v>
       </c>
-      <c r="F7" s="123"/>
-      <c r="G7" s="123"/>
-      <c r="H7" s="123"/>
-      <c r="I7" s="123"/>
-      <c r="J7" s="122" t="s">
+      <c r="F7" s="113"/>
+      <c r="G7" s="113"/>
+      <c r="H7" s="113"/>
+      <c r="I7" s="113"/>
+      <c r="J7" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="K7" s="122" t="s">
+      <c r="K7" s="113" t="s">
         <v>44</v>
       </c>
-      <c r="L7" s="122" t="s">
+      <c r="L7" s="113" t="s">
         <v>45</v>
       </c>
-      <c r="M7" s="121" t="s">
+      <c r="M7" s="112" t="s">
         <v>46</v>
       </c>
-      <c r="N7" s="122" t="s">
+      <c r="N7" s="113" t="s">
         <v>47</v>
       </c>
-      <c r="O7" s="140" t="s">
+      <c r="O7" s="114" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:15">
-      <c r="A8" s="124">
-        <v>1</v>
-      </c>
-      <c r="B8" s="125" t="s">
+      <c r="A8" s="115">
+        <v>1</v>
+      </c>
+      <c r="B8" s="116" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="126" t="s">
+      <c r="C8" s="117" t="s">
         <v>50</v>
       </c>
-      <c r="D8" s="32" t="s">
+      <c r="D8" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="E8" s="127" t="s">
+      <c r="E8" s="118" t="s">
         <v>52</v>
       </c>
-      <c r="F8" s="127"/>
-      <c r="G8" s="127"/>
-      <c r="H8" s="127"/>
-      <c r="I8" s="127"/>
-      <c r="J8" s="141">
+      <c r="F8" s="118"/>
+      <c r="G8" s="118"/>
+      <c r="H8" s="118"/>
+      <c r="I8" s="118"/>
+      <c r="J8" s="119">
         <v>10</v>
       </c>
-      <c r="K8" s="134">
+      <c r="K8" s="120">
         <v>12</v>
       </c>
-      <c r="L8" s="142" t="s">
+      <c r="L8" s="121" t="s">
         <v>53</v>
       </c>
-      <c r="M8" s="143" t="s">
+      <c r="M8" s="122" t="s">
         <v>54</v>
       </c>
-      <c r="N8" s="126" t="s">
+      <c r="N8" s="117" t="s">
         <v>55</v>
       </c>
-      <c r="O8" s="144">
+      <c r="O8" s="123">
         <v>43763.4969328704</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:15">
-      <c r="A9" s="124"/>
-      <c r="B9" s="125"/>
-      <c r="C9" s="126"/>
-      <c r="D9" s="32" t="s">
+      <c r="A9" s="115"/>
+      <c r="B9" s="116"/>
+      <c r="C9" s="117"/>
+      <c r="D9" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="E9" s="127" t="s">
+      <c r="E9" s="118" t="s">
         <v>52</v>
       </c>
-      <c r="F9" s="127"/>
-      <c r="G9" s="127"/>
-      <c r="H9" s="127"/>
-      <c r="I9" s="127"/>
-      <c r="J9" s="141">
+      <c r="F9" s="118"/>
+      <c r="G9" s="118"/>
+      <c r="H9" s="118"/>
+      <c r="I9" s="118"/>
+      <c r="J9" s="119">
         <v>20</v>
       </c>
-      <c r="K9" s="134">
+      <c r="K9" s="120">
         <v>13</v>
       </c>
-      <c r="L9" s="145"/>
-      <c r="M9" s="146"/>
-      <c r="N9" s="126"/>
-      <c r="O9" s="144"/>
+      <c r="L9" s="124"/>
+      <c r="M9" s="125"/>
+      <c r="N9" s="117"/>
+      <c r="O9" s="123"/>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:15">
-      <c r="A10" s="124"/>
-      <c r="B10" s="125"/>
-      <c r="C10" s="126"/>
-      <c r="D10" s="32" t="s">
+      <c r="A10" s="115"/>
+      <c r="B10" s="116"/>
+      <c r="C10" s="117"/>
+      <c r="D10" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="E10" s="127" t="s">
+      <c r="E10" s="118" t="s">
         <v>52</v>
       </c>
-      <c r="F10" s="127"/>
-      <c r="G10" s="127"/>
-      <c r="H10" s="127"/>
-      <c r="I10" s="127"/>
-      <c r="J10" s="141">
+      <c r="F10" s="118"/>
+      <c r="G10" s="118"/>
+      <c r="H10" s="118"/>
+      <c r="I10" s="118"/>
+      <c r="J10" s="119">
         <v>20</v>
       </c>
-      <c r="K10" s="134">
+      <c r="K10" s="120">
         <v>14</v>
       </c>
-      <c r="L10" s="145"/>
-      <c r="M10" s="146"/>
-      <c r="N10" s="126"/>
-      <c r="O10" s="144"/>
+      <c r="L10" s="124"/>
+      <c r="M10" s="125"/>
+      <c r="N10" s="117"/>
+      <c r="O10" s="123"/>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:15">
-      <c r="A11" s="124"/>
-      <c r="B11" s="125"/>
-      <c r="C11" s="126"/>
-      <c r="D11" s="32" t="s">
+      <c r="A11" s="115"/>
+      <c r="B11" s="116"/>
+      <c r="C11" s="117"/>
+      <c r="D11" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="E11" s="127" t="s">
+      <c r="E11" s="118" t="s">
         <v>52</v>
       </c>
-      <c r="F11" s="127"/>
-      <c r="G11" s="127"/>
-      <c r="H11" s="127"/>
-      <c r="I11" s="127"/>
-      <c r="J11" s="141">
+      <c r="F11" s="118"/>
+      <c r="G11" s="118"/>
+      <c r="H11" s="118"/>
+      <c r="I11" s="118"/>
+      <c r="J11" s="119">
         <v>35</v>
       </c>
-      <c r="K11" s="134">
+      <c r="K11" s="120">
         <v>15</v>
       </c>
-      <c r="L11" s="145"/>
-      <c r="M11" s="146"/>
-      <c r="N11" s="126"/>
-      <c r="O11" s="144"/>
+      <c r="L11" s="124"/>
+      <c r="M11" s="125"/>
+      <c r="N11" s="117"/>
+      <c r="O11" s="123"/>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:15">
-      <c r="A12" s="128">
+      <c r="A12" s="126">
         <v>2</v>
       </c>
-      <c r="B12" s="129" t="s">
+      <c r="B12" s="127" t="s">
         <v>49</v>
       </c>
-      <c r="C12" s="130" t="s">
+      <c r="C12" s="128" t="s">
         <v>50</v>
       </c>
-      <c r="D12" s="34" t="s">
+      <c r="D12" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="E12" s="131"/>
-      <c r="F12" s="131"/>
-      <c r="G12" s="131"/>
-      <c r="H12" s="131"/>
-      <c r="I12" s="131"/>
-      <c r="J12" s="130">
-        <v>1</v>
-      </c>
-      <c r="K12" s="130">
-        <v>1</v>
-      </c>
-      <c r="L12" s="147" t="s">
+      <c r="E12" s="129"/>
+      <c r="F12" s="129"/>
+      <c r="G12" s="129"/>
+      <c r="H12" s="129"/>
+      <c r="I12" s="129"/>
+      <c r="J12" s="128">
+        <v>1</v>
+      </c>
+      <c r="K12" s="128">
+        <v>1</v>
+      </c>
+      <c r="L12" s="130" t="s">
         <v>60</v>
       </c>
-      <c r="M12" s="148" t="s">
+      <c r="M12" s="131" t="s">
         <v>61</v>
       </c>
-      <c r="N12" s="130" t="s">
+      <c r="N12" s="128" t="s">
         <v>55</v>
       </c>
-      <c r="O12" s="149">
+      <c r="O12" s="132">
         <v>43763.4969328704</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:15">
-      <c r="A13" s="132">
+      <c r="A13" s="115">
         <v>3</v>
       </c>
       <c r="B13" s="133" t="s">
         <v>62</v>
       </c>
-      <c r="C13" s="134" t="s">
+      <c r="C13" s="120" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="32" t="s">
+      <c r="D13" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="127" t="s">
+      <c r="E13" s="118" t="s">
         <v>63</v>
       </c>
-      <c r="F13" s="127"/>
-      <c r="G13" s="127"/>
-      <c r="H13" s="127"/>
-      <c r="I13" s="127"/>
-      <c r="J13" s="134">
-        <v>1</v>
-      </c>
-      <c r="K13" s="134">
-        <v>1</v>
-      </c>
-      <c r="L13" s="150" t="s">
+      <c r="F13" s="118"/>
+      <c r="G13" s="118"/>
+      <c r="H13" s="118"/>
+      <c r="I13" s="118"/>
+      <c r="J13" s="120">
+        <v>1</v>
+      </c>
+      <c r="K13" s="120">
+        <v>1</v>
+      </c>
+      <c r="L13" s="134" t="s">
         <v>60</v>
       </c>
-      <c r="M13" s="151" t="s">
+      <c r="M13" s="135" t="s">
         <v>61</v>
       </c>
-      <c r="N13" s="134" t="s">
+      <c r="N13" s="120" t="s">
         <v>64</v>
       </c>
-      <c r="O13" s="152">
+      <c r="O13" s="123">
         <v>43763.4969328704</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:15">
-      <c r="A14" s="128">
+      <c r="A14" s="126">
         <v>4</v>
       </c>
-      <c r="B14" s="129" t="s">
+      <c r="B14" s="127" t="s">
         <v>65</v>
       </c>
-      <c r="C14" s="130" t="s">
+      <c r="C14" s="128" t="s">
         <v>50</v>
       </c>
-      <c r="D14" s="34" t="s">
+      <c r="D14" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="E14" s="131" t="s">
+      <c r="E14" s="129" t="s">
         <v>67</v>
       </c>
-      <c r="F14" s="131"/>
-      <c r="G14" s="131"/>
-      <c r="H14" s="131"/>
-      <c r="I14" s="131"/>
-      <c r="J14" s="130">
-        <v>1</v>
-      </c>
-      <c r="K14" s="130">
-        <v>1</v>
-      </c>
-      <c r="L14" s="147" t="s">
+      <c r="F14" s="129"/>
+      <c r="G14" s="129"/>
+      <c r="H14" s="129"/>
+      <c r="I14" s="129"/>
+      <c r="J14" s="128">
+        <v>1</v>
+      </c>
+      <c r="K14" s="128">
+        <v>1</v>
+      </c>
+      <c r="L14" s="130" t="s">
         <v>60</v>
       </c>
-      <c r="M14" s="148" t="s">
+      <c r="M14" s="131" t="s">
         <v>61</v>
       </c>
-      <c r="N14" s="130" t="s">
+      <c r="N14" s="128" t="s">
         <v>64</v>
       </c>
-      <c r="O14" s="149">
+      <c r="O14" s="132">
         <v>43764.4969328704</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:15">
-      <c r="A15" s="132">
+      <c r="A15" s="115">
         <v>5</v>
       </c>
       <c r="B15" s="133" t="s">
         <v>68</v>
       </c>
-      <c r="C15" s="134" t="s">
+      <c r="C15" s="120" t="s">
         <v>50</v>
       </c>
-      <c r="D15" s="32" t="s">
+      <c r="D15" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="E15" s="127" t="s">
+      <c r="E15" s="118" t="s">
         <v>52</v>
       </c>
-      <c r="F15" s="127"/>
-      <c r="G15" s="127"/>
-      <c r="H15" s="127"/>
-      <c r="I15" s="127"/>
-      <c r="J15" s="134">
-        <v>1</v>
-      </c>
-      <c r="K15" s="134">
-        <v>1</v>
-      </c>
-      <c r="L15" s="150" t="s">
+      <c r="F15" s="118"/>
+      <c r="G15" s="118"/>
+      <c r="H15" s="118"/>
+      <c r="I15" s="118"/>
+      <c r="J15" s="120">
+        <v>1</v>
+      </c>
+      <c r="K15" s="120">
+        <v>1</v>
+      </c>
+      <c r="L15" s="134" t="s">
         <v>60</v>
       </c>
-      <c r="M15" s="151" t="s">
+      <c r="M15" s="135" t="s">
         <v>61</v>
       </c>
-      <c r="N15" s="134" t="s">
+      <c r="N15" s="120" t="s">
         <v>64</v>
       </c>
-      <c r="O15" s="152">
+      <c r="O15" s="123">
         <v>43765.4969328704</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:15">
-      <c r="A16" s="128">
+      <c r="A16" s="126">
         <v>6</v>
       </c>
-      <c r="B16" s="129" t="s">
+      <c r="B16" s="127" t="s">
         <v>70</v>
       </c>
-      <c r="C16" s="130" t="s">
+      <c r="C16" s="128" t="s">
         <v>50</v>
       </c>
-      <c r="D16" s="34" t="s">
+      <c r="D16" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="E16" s="131" t="s">
+      <c r="E16" s="129" t="s">
         <v>52</v>
       </c>
-      <c r="F16" s="131"/>
-      <c r="G16" s="131"/>
-      <c r="H16" s="131"/>
-      <c r="I16" s="131"/>
-      <c r="J16" s="130">
-        <v>1</v>
-      </c>
-      <c r="K16" s="130">
-        <v>1</v>
-      </c>
-      <c r="L16" s="147" t="s">
+      <c r="F16" s="129"/>
+      <c r="G16" s="129"/>
+      <c r="H16" s="129"/>
+      <c r="I16" s="129"/>
+      <c r="J16" s="128">
+        <v>1</v>
+      </c>
+      <c r="K16" s="128">
+        <v>1</v>
+      </c>
+      <c r="L16" s="130" t="s">
         <v>60</v>
       </c>
-      <c r="M16" s="148" t="s">
+      <c r="M16" s="131" t="s">
         <v>61</v>
       </c>
-      <c r="N16" s="130" t="s">
+      <c r="N16" s="128" t="s">
         <v>64</v>
       </c>
-      <c r="O16" s="149">
+      <c r="O16" s="132">
         <v>43766.4969328704</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:15">
-      <c r="A17" s="132">
+      <c r="A17" s="115">
         <v>7</v>
       </c>
       <c r="B17" s="133" t="s">
         <v>72</v>
       </c>
-      <c r="C17" s="134" t="s">
+      <c r="C17" s="120" t="s">
         <v>50</v>
       </c>
-      <c r="D17" s="32" t="s">
+      <c r="D17" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="E17" s="127" t="s">
+      <c r="E17" s="118" t="s">
         <v>52</v>
       </c>
-      <c r="F17" s="127"/>
-      <c r="G17" s="127"/>
-      <c r="H17" s="127"/>
-      <c r="I17" s="127"/>
-      <c r="J17" s="134">
-        <v>1</v>
-      </c>
-      <c r="K17" s="134">
-        <v>1</v>
-      </c>
-      <c r="L17" s="150" t="s">
+      <c r="F17" s="118"/>
+      <c r="G17" s="118"/>
+      <c r="H17" s="118"/>
+      <c r="I17" s="118"/>
+      <c r="J17" s="120">
+        <v>1</v>
+      </c>
+      <c r="K17" s="120">
+        <v>1</v>
+      </c>
+      <c r="L17" s="134" t="s">
         <v>60</v>
       </c>
-      <c r="M17" s="151" t="s">
+      <c r="M17" s="135" t="s">
         <v>61</v>
       </c>
-      <c r="N17" s="134" t="s">
+      <c r="N17" s="120" t="s">
         <v>64</v>
       </c>
-      <c r="O17" s="152">
+      <c r="O17" s="123">
         <v>43767.4969328704</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:15">
-      <c r="A18" s="128">
+      <c r="A18" s="126">
         <v>8</v>
       </c>
-      <c r="B18" s="129" t="s">
+      <c r="B18" s="127" t="s">
         <v>74</v>
       </c>
-      <c r="C18" s="130" t="s">
+      <c r="C18" s="128" t="s">
         <v>50</v>
       </c>
-      <c r="D18" s="34" t="s">
+      <c r="D18" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="E18" s="131" t="s">
+      <c r="E18" s="129" t="s">
         <v>52</v>
       </c>
-      <c r="F18" s="131"/>
-      <c r="G18" s="131"/>
-      <c r="H18" s="131"/>
-      <c r="I18" s="131"/>
-      <c r="J18" s="130">
-        <v>1</v>
-      </c>
-      <c r="K18" s="130">
-        <v>1</v>
-      </c>
-      <c r="L18" s="147" t="s">
+      <c r="F18" s="129"/>
+      <c r="G18" s="129"/>
+      <c r="H18" s="129"/>
+      <c r="I18" s="129"/>
+      <c r="J18" s="128">
+        <v>1</v>
+      </c>
+      <c r="K18" s="128">
+        <v>1</v>
+      </c>
+      <c r="L18" s="130" t="s">
         <v>60</v>
       </c>
-      <c r="M18" s="148" t="s">
+      <c r="M18" s="131" t="s">
         <v>61</v>
       </c>
-      <c r="N18" s="130" t="s">
+      <c r="N18" s="128" t="s">
         <v>64</v>
       </c>
-      <c r="O18" s="149">
+      <c r="O18" s="132">
         <v>43768.4969328704</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:15">
-      <c r="A19" s="132">
+      <c r="A19" s="115">
         <v>9</v>
       </c>
       <c r="B19" s="133" t="s">
         <v>76</v>
       </c>
-      <c r="C19" s="134" t="s">
+      <c r="C19" s="120" t="s">
         <v>50</v>
       </c>
-      <c r="D19" s="32" t="s">
+      <c r="D19" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="E19" s="127" t="s">
+      <c r="E19" s="118" t="s">
         <v>52</v>
       </c>
-      <c r="F19" s="127"/>
-      <c r="G19" s="127"/>
-      <c r="H19" s="127"/>
-      <c r="I19" s="127"/>
-      <c r="J19" s="134">
-        <v>1</v>
-      </c>
-      <c r="K19" s="134">
-        <v>1</v>
-      </c>
-      <c r="L19" s="150" t="s">
+      <c r="F19" s="118"/>
+      <c r="G19" s="118"/>
+      <c r="H19" s="118"/>
+      <c r="I19" s="118"/>
+      <c r="J19" s="120">
+        <v>1</v>
+      </c>
+      <c r="K19" s="120">
+        <v>1</v>
+      </c>
+      <c r="L19" s="134" t="s">
         <v>60</v>
       </c>
-      <c r="M19" s="151" t="s">
+      <c r="M19" s="135" t="s">
         <v>61</v>
       </c>
-      <c r="N19" s="134" t="s">
+      <c r="N19" s="120" t="s">
         <v>64</v>
       </c>
-      <c r="O19" s="152">
+      <c r="O19" s="123">
         <v>43769.4969328704</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:15">
-      <c r="A20" s="128">
+      <c r="A20" s="126">
         <v>10</v>
       </c>
-      <c r="B20" s="129" t="s">
+      <c r="B20" s="127" t="s">
         <v>78</v>
       </c>
-      <c r="C20" s="130" t="s">
+      <c r="C20" s="128" t="s">
         <v>50</v>
       </c>
-      <c r="D20" s="34" t="s">
+      <c r="D20" s="23" t="s">
         <v>79</v>
       </c>
-      <c r="E20" s="131" t="s">
+      <c r="E20" s="129" t="s">
         <v>52</v>
       </c>
-      <c r="F20" s="131"/>
-      <c r="G20" s="131"/>
-      <c r="H20" s="131"/>
-      <c r="I20" s="131"/>
-      <c r="J20" s="130">
-        <v>1</v>
-      </c>
-      <c r="K20" s="130">
-        <v>1</v>
-      </c>
-      <c r="L20" s="147" t="s">
+      <c r="F20" s="129"/>
+      <c r="G20" s="129"/>
+      <c r="H20" s="129"/>
+      <c r="I20" s="129"/>
+      <c r="J20" s="128">
+        <v>1</v>
+      </c>
+      <c r="K20" s="128">
+        <v>1</v>
+      </c>
+      <c r="L20" s="130" t="s">
         <v>60</v>
       </c>
-      <c r="M20" s="148" t="s">
+      <c r="M20" s="131" t="s">
         <v>61</v>
       </c>
-      <c r="N20" s="130" t="s">
+      <c r="N20" s="128" t="s">
         <v>64</v>
       </c>
-      <c r="O20" s="149">
+      <c r="O20" s="132">
         <v>43770.4969328704</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" spans="1:15">
-      <c r="A21" s="132">
+      <c r="A21" s="115">
         <v>11</v>
       </c>
       <c r="B21" s="133" t="s">
         <v>80</v>
       </c>
-      <c r="C21" s="134" t="s">
+      <c r="C21" s="120" t="s">
         <v>50</v>
       </c>
-      <c r="D21" s="32" t="s">
+      <c r="D21" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="E21" s="127" t="s">
+      <c r="E21" s="118" t="s">
         <v>52</v>
       </c>
-      <c r="F21" s="127"/>
-      <c r="G21" s="127"/>
-      <c r="H21" s="127"/>
-      <c r="I21" s="127"/>
-      <c r="J21" s="134">
-        <v>1</v>
-      </c>
-      <c r="K21" s="134">
-        <v>1</v>
-      </c>
-      <c r="L21" s="150" t="s">
+      <c r="F21" s="118"/>
+      <c r="G21" s="118"/>
+      <c r="H21" s="118"/>
+      <c r="I21" s="118"/>
+      <c r="J21" s="120">
+        <v>1</v>
+      </c>
+      <c r="K21" s="120">
+        <v>1</v>
+      </c>
+      <c r="L21" s="134" t="s">
         <v>60</v>
       </c>
-      <c r="M21" s="151" t="s">
+      <c r="M21" s="135" t="s">
         <v>61</v>
       </c>
-      <c r="N21" s="134" t="s">
+      <c r="N21" s="120" t="s">
         <v>64</v>
       </c>
-      <c r="O21" s="152">
+      <c r="O21" s="123">
         <v>43771.4969328704</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" spans="1:15">
-      <c r="A22" s="128">
+      <c r="A22" s="126">
         <v>12</v>
       </c>
-      <c r="B22" s="129" t="s">
+      <c r="B22" s="127" t="s">
         <v>82</v>
       </c>
-      <c r="C22" s="130" t="s">
+      <c r="C22" s="128" t="s">
         <v>50</v>
       </c>
-      <c r="D22" s="34" t="s">
+      <c r="D22" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="E22" s="131" t="s">
+      <c r="E22" s="129" t="s">
         <v>52</v>
       </c>
-      <c r="F22" s="131"/>
-      <c r="G22" s="131"/>
-      <c r="H22" s="131"/>
-      <c r="I22" s="131"/>
-      <c r="J22" s="130">
-        <v>1</v>
-      </c>
-      <c r="K22" s="130">
-        <v>1</v>
-      </c>
-      <c r="L22" s="147" t="s">
+      <c r="F22" s="129"/>
+      <c r="G22" s="129"/>
+      <c r="H22" s="129"/>
+      <c r="I22" s="129"/>
+      <c r="J22" s="128">
+        <v>1</v>
+      </c>
+      <c r="K22" s="128">
+        <v>1</v>
+      </c>
+      <c r="L22" s="130" t="s">
         <v>60</v>
       </c>
-      <c r="M22" s="148" t="s">
+      <c r="M22" s="131" t="s">
         <v>61</v>
       </c>
-      <c r="N22" s="130" t="s">
+      <c r="N22" s="128" t="s">
         <v>64</v>
       </c>
-      <c r="O22" s="149">
+      <c r="O22" s="132">
         <v>43772.4969328704</v>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" spans="1:15">
-      <c r="A23" s="132">
+      <c r="A23" s="115">
         <v>13</v>
       </c>
       <c r="B23" s="133" t="s">
         <v>84</v>
       </c>
-      <c r="C23" s="134" t="s">
+      <c r="C23" s="120" t="s">
         <v>50</v>
       </c>
-      <c r="D23" s="32" t="s">
+      <c r="D23" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="E23" s="127" t="s">
+      <c r="E23" s="118" t="s">
         <v>52</v>
       </c>
-      <c r="F23" s="127"/>
-      <c r="G23" s="127"/>
-      <c r="H23" s="127"/>
-      <c r="I23" s="127"/>
-      <c r="J23" s="134">
-        <v>1</v>
-      </c>
-      <c r="K23" s="134">
-        <v>1</v>
-      </c>
-      <c r="L23" s="150" t="s">
+      <c r="F23" s="118"/>
+      <c r="G23" s="118"/>
+      <c r="H23" s="118"/>
+      <c r="I23" s="118"/>
+      <c r="J23" s="120">
+        <v>1</v>
+      </c>
+      <c r="K23" s="120">
+        <v>1</v>
+      </c>
+      <c r="L23" s="134" t="s">
         <v>60</v>
       </c>
-      <c r="M23" s="151" t="s">
+      <c r="M23" s="135" t="s">
         <v>61</v>
       </c>
-      <c r="N23" s="134" t="s">
+      <c r="N23" s="120" t="s">
         <v>64</v>
       </c>
-      <c r="O23" s="152">
+      <c r="O23" s="123">
         <v>43773.4969328704</v>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1" spans="1:15">
-      <c r="A24" s="128">
+      <c r="A24" s="126">
         <v>14</v>
       </c>
-      <c r="B24" s="129" t="s">
+      <c r="B24" s="127" t="s">
         <v>86</v>
       </c>
-      <c r="C24" s="130" t="s">
+      <c r="C24" s="128" t="s">
         <v>50</v>
       </c>
-      <c r="D24" s="34" t="s">
+      <c r="D24" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="E24" s="131" t="s">
+      <c r="E24" s="129" t="s">
         <v>52</v>
       </c>
-      <c r="F24" s="131"/>
-      <c r="G24" s="131"/>
-      <c r="H24" s="131"/>
-      <c r="I24" s="131"/>
-      <c r="J24" s="130">
-        <v>1</v>
-      </c>
-      <c r="K24" s="130">
-        <v>1</v>
-      </c>
-      <c r="L24" s="147" t="s">
+      <c r="F24" s="129"/>
+      <c r="G24" s="129"/>
+      <c r="H24" s="129"/>
+      <c r="I24" s="129"/>
+      <c r="J24" s="128">
+        <v>1</v>
+      </c>
+      <c r="K24" s="128">
+        <v>1</v>
+      </c>
+      <c r="L24" s="130" t="s">
         <v>60</v>
       </c>
-      <c r="M24" s="148" t="s">
+      <c r="M24" s="131" t="s">
         <v>61</v>
       </c>
-      <c r="N24" s="130" t="s">
+      <c r="N24" s="128" t="s">
         <v>64</v>
       </c>
-      <c r="O24" s="149">
+      <c r="O24" s="132">
         <v>43774.4969328704</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" spans="1:15">
-      <c r="A25" s="132">
+      <c r="A25" s="115">
         <v>15</v>
       </c>
       <c r="B25" s="133" t="s">
         <v>88</v>
       </c>
-      <c r="C25" s="134" t="s">
+      <c r="C25" s="120" t="s">
         <v>50</v>
       </c>
-      <c r="D25" s="32" t="s">
+      <c r="D25" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="E25" s="127" t="s">
+      <c r="E25" s="118" t="s">
         <v>52</v>
       </c>
-      <c r="F25" s="127"/>
-      <c r="G25" s="127"/>
-      <c r="H25" s="127"/>
-      <c r="I25" s="127"/>
-      <c r="J25" s="134">
-        <v>1</v>
-      </c>
-      <c r="K25" s="134">
-        <v>1</v>
-      </c>
-      <c r="L25" s="150" t="s">
+      <c r="F25" s="118"/>
+      <c r="G25" s="118"/>
+      <c r="H25" s="118"/>
+      <c r="I25" s="118"/>
+      <c r="J25" s="120">
+        <v>1</v>
+      </c>
+      <c r="K25" s="120">
+        <v>1</v>
+      </c>
+      <c r="L25" s="134" t="s">
         <v>60</v>
       </c>
-      <c r="M25" s="151" t="s">
+      <c r="M25" s="135" t="s">
         <v>61</v>
       </c>
-      <c r="N25" s="134" t="s">
+      <c r="N25" s="120" t="s">
         <v>64</v>
       </c>
-      <c r="O25" s="152">
+      <c r="O25" s="123">
         <v>43775.4969328704</v>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1" spans="1:15">
-      <c r="A26" s="128">
+      <c r="A26" s="126">
         <v>16</v>
       </c>
-      <c r="B26" s="129" t="s">
+      <c r="B26" s="127" t="s">
         <v>90</v>
       </c>
-      <c r="C26" s="130" t="s">
+      <c r="C26" s="128" t="s">
         <v>50</v>
       </c>
-      <c r="D26" s="34" t="s">
+      <c r="D26" s="23" t="s">
         <v>91</v>
       </c>
-      <c r="E26" s="131" t="s">
+      <c r="E26" s="129" t="s">
         <v>52</v>
       </c>
-      <c r="F26" s="131"/>
-      <c r="G26" s="131"/>
-      <c r="H26" s="131"/>
-      <c r="I26" s="131"/>
-      <c r="J26" s="130">
-        <v>1</v>
-      </c>
-      <c r="K26" s="130">
-        <v>1</v>
-      </c>
-      <c r="L26" s="147" t="s">
+      <c r="F26" s="129"/>
+      <c r="G26" s="129"/>
+      <c r="H26" s="129"/>
+      <c r="I26" s="129"/>
+      <c r="J26" s="128">
+        <v>1</v>
+      </c>
+      <c r="K26" s="128">
+        <v>1</v>
+      </c>
+      <c r="L26" s="130" t="s">
         <v>60</v>
       </c>
-      <c r="M26" s="148" t="s">
+      <c r="M26" s="131" t="s">
         <v>61</v>
       </c>
-      <c r="N26" s="130" t="s">
+      <c r="N26" s="128" t="s">
         <v>64</v>
       </c>
-      <c r="O26" s="149">
+      <c r="O26" s="132">
         <v>43776.4969328704</v>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1" spans="1:15">
-      <c r="A27" s="132">
+      <c r="A27" s="115">
         <v>17</v>
       </c>
       <c r="B27" s="133" t="s">
         <v>92</v>
       </c>
-      <c r="C27" s="134" t="s">
+      <c r="C27" s="120" t="s">
         <v>50</v>
       </c>
-      <c r="D27" s="32" t="s">
+      <c r="D27" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="E27" s="127" t="s">
+      <c r="E27" s="118" t="s">
         <v>52</v>
       </c>
-      <c r="F27" s="127"/>
-      <c r="G27" s="127"/>
-      <c r="H27" s="127"/>
-      <c r="I27" s="127"/>
-      <c r="J27" s="134">
-        <v>1</v>
-      </c>
-      <c r="K27" s="134">
-        <v>1</v>
-      </c>
-      <c r="L27" s="150" t="s">
+      <c r="F27" s="118"/>
+      <c r="G27" s="118"/>
+      <c r="H27" s="118"/>
+      <c r="I27" s="118"/>
+      <c r="J27" s="120">
+        <v>1</v>
+      </c>
+      <c r="K27" s="120">
+        <v>1</v>
+      </c>
+      <c r="L27" s="134" t="s">
         <v>60</v>
       </c>
-      <c r="M27" s="151" t="s">
+      <c r="M27" s="135" t="s">
         <v>61</v>
       </c>
-      <c r="N27" s="134" t="s">
+      <c r="N27" s="120" t="s">
         <v>64</v>
       </c>
-      <c r="O27" s="152">
+      <c r="O27" s="123">
         <v>43777.4969328704</v>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1" spans="1:15">
-      <c r="A28" s="128">
+      <c r="A28" s="126">
         <v>18</v>
       </c>
-      <c r="B28" s="129" t="s">
+      <c r="B28" s="127" t="s">
         <v>94</v>
       </c>
-      <c r="C28" s="130" t="s">
+      <c r="C28" s="128" t="s">
         <v>50</v>
       </c>
-      <c r="D28" s="34" t="s">
+      <c r="D28" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="E28" s="131" t="s">
+      <c r="E28" s="129" t="s">
         <v>52</v>
       </c>
-      <c r="F28" s="131"/>
-      <c r="G28" s="131"/>
-      <c r="H28" s="131"/>
-      <c r="I28" s="131"/>
-      <c r="J28" s="130">
-        <v>1</v>
-      </c>
-      <c r="K28" s="130">
-        <v>1</v>
-      </c>
-      <c r="L28" s="147" t="s">
+      <c r="F28" s="129"/>
+      <c r="G28" s="129"/>
+      <c r="H28" s="129"/>
+      <c r="I28" s="129"/>
+      <c r="J28" s="128">
+        <v>1</v>
+      </c>
+      <c r="K28" s="128">
+        <v>1</v>
+      </c>
+      <c r="L28" s="130" t="s">
         <v>60</v>
       </c>
-      <c r="M28" s="148" t="s">
+      <c r="M28" s="131" t="s">
         <v>61</v>
       </c>
-      <c r="N28" s="130" t="s">
+      <c r="N28" s="128" t="s">
         <v>64</v>
       </c>
-      <c r="O28" s="149">
+      <c r="O28" s="132">
         <v>43778.4969328704</v>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1" spans="1:15">
-      <c r="A29" s="132">
+      <c r="A29" s="115">
         <v>19</v>
       </c>
       <c r="B29" s="133" t="s">
         <v>96</v>
       </c>
-      <c r="C29" s="134" t="s">
+      <c r="C29" s="120" t="s">
         <v>50</v>
       </c>
-      <c r="D29" s="32" t="s">
+      <c r="D29" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="E29" s="127" t="s">
+      <c r="E29" s="118" t="s">
         <v>52</v>
       </c>
-      <c r="F29" s="127"/>
-      <c r="G29" s="127"/>
-      <c r="H29" s="127"/>
-      <c r="I29" s="127"/>
-      <c r="J29" s="134">
-        <v>1</v>
-      </c>
-      <c r="K29" s="134">
-        <v>1</v>
-      </c>
-      <c r="L29" s="150" t="s">
+      <c r="F29" s="118"/>
+      <c r="G29" s="118"/>
+      <c r="H29" s="118"/>
+      <c r="I29" s="118"/>
+      <c r="J29" s="120">
+        <v>1</v>
+      </c>
+      <c r="K29" s="120">
+        <v>1</v>
+      </c>
+      <c r="L29" s="134" t="s">
         <v>60</v>
       </c>
-      <c r="M29" s="151" t="s">
+      <c r="M29" s="135" t="s">
         <v>61</v>
       </c>
-      <c r="N29" s="134" t="s">
+      <c r="N29" s="120" t="s">
         <v>64</v>
       </c>
-      <c r="O29" s="152">
+      <c r="O29" s="123">
         <v>43779.4969328704</v>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1" spans="1:15">
-      <c r="A30" s="128">
+      <c r="A30" s="126">
         <v>20</v>
       </c>
-      <c r="B30" s="129" t="s">
+      <c r="B30" s="127" t="s">
         <v>98</v>
       </c>
-      <c r="C30" s="130" t="s">
+      <c r="C30" s="128" t="s">
         <v>50</v>
       </c>
-      <c r="D30" s="34" t="s">
+      <c r="D30" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="E30" s="131" t="s">
+      <c r="E30" s="129" t="s">
         <v>52</v>
       </c>
-      <c r="F30" s="131"/>
-      <c r="G30" s="131"/>
-      <c r="H30" s="131"/>
-      <c r="I30" s="131"/>
-      <c r="J30" s="130">
-        <v>1</v>
-      </c>
-      <c r="K30" s="130">
-        <v>1</v>
-      </c>
-      <c r="L30" s="147" t="s">
+      <c r="F30" s="129"/>
+      <c r="G30" s="129"/>
+      <c r="H30" s="129"/>
+      <c r="I30" s="129"/>
+      <c r="J30" s="128">
+        <v>1</v>
+      </c>
+      <c r="K30" s="128">
+        <v>1</v>
+      </c>
+      <c r="L30" s="130" t="s">
         <v>60</v>
       </c>
-      <c r="M30" s="148" t="s">
+      <c r="M30" s="131" t="s">
         <v>61</v>
       </c>
-      <c r="N30" s="130" t="s">
+      <c r="N30" s="128" t="s">
         <v>64</v>
       </c>
-      <c r="O30" s="149">
+      <c r="O30" s="132">
         <v>43780.4969328704</v>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1" spans="1:15">
-      <c r="A31" s="135"/>
-      <c r="B31" s="136"/>
-      <c r="C31" s="137"/>
-      <c r="D31" s="137"/>
-      <c r="E31" s="137"/>
-      <c r="F31" s="137"/>
-      <c r="G31" s="137"/>
-      <c r="H31" s="137"/>
-      <c r="I31" s="137"/>
-      <c r="J31" s="137"/>
-      <c r="K31" s="137"/>
-      <c r="L31" s="137"/>
-      <c r="M31" s="136"/>
-      <c r="N31" s="137"/>
-      <c r="O31" s="153"/>
+      <c r="A31" s="136"/>
+      <c r="B31" s="137"/>
+      <c r="C31" s="138"/>
+      <c r="D31" s="138"/>
+      <c r="E31" s="138"/>
+      <c r="F31" s="138"/>
+      <c r="G31" s="138"/>
+      <c r="H31" s="138"/>
+      <c r="I31" s="138"/>
+      <c r="J31" s="138"/>
+      <c r="K31" s="138"/>
+      <c r="L31" s="138"/>
+      <c r="M31" s="137"/>
+      <c r="N31" s="138"/>
+      <c r="O31" s="139"/>
     </row>
   </sheetData>
   <mergeCells count="33">
@@ -4095,7 +4276,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A5:K18"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="2" width="15.625" customWidth="1"/>
     <col min="3" max="3" width="20.625" customWidth="1"/>
@@ -4105,413 +4286,413 @@
     <col min="8" max="11" width="15.625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" s="66" customFormat="1" ht="30" customHeight="1" spans="1:11">
-      <c r="A5" s="68" t="s">
+    <row r="5" s="59" customFormat="1" ht="30" customHeight="1" spans="1:11">
+      <c r="A5" s="61" t="s">
         <v>100</v>
       </c>
-      <c r="B5" s="70"/>
-      <c r="C5" s="70"/>
-      <c r="D5" s="70"/>
-      <c r="E5" s="70"/>
-      <c r="F5" s="70"/>
-      <c r="G5" s="70"/>
-      <c r="H5" s="71"/>
-      <c r="I5" s="71"/>
-      <c r="J5" s="71"/>
-      <c r="K5" s="71"/>
-    </row>
-    <row r="6" s="66" customFormat="1" ht="30" customHeight="1" spans="1:11">
-      <c r="A6" s="91" t="s">
+      <c r="B5" s="62"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="63"/>
+      <c r="I5" s="63"/>
+      <c r="J5" s="63"/>
+      <c r="K5" s="63"/>
+    </row>
+    <row r="6" s="59" customFormat="1" ht="30" customHeight="1" spans="1:11">
+      <c r="A6" s="80" t="s">
         <v>101</v>
       </c>
-      <c r="B6" s="92" t="s">
+      <c r="B6" s="81" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="92" t="s">
+      <c r="C6" s="81" t="s">
         <v>103</v>
       </c>
-      <c r="D6" s="93"/>
-      <c r="E6" s="93"/>
-      <c r="F6" s="93"/>
-      <c r="G6" s="93"/>
-      <c r="H6" s="94"/>
-      <c r="I6" s="94"/>
-      <c r="J6" s="94"/>
-      <c r="K6" s="98"/>
-    </row>
-    <row r="7" s="67" customFormat="1" ht="30" customHeight="1" spans="1:11">
-      <c r="A7" s="95" t="s">
+      <c r="D6" s="82"/>
+      <c r="E6" s="82"/>
+      <c r="F6" s="82"/>
+      <c r="G6" s="82"/>
+      <c r="H6" s="83"/>
+      <c r="I6" s="83"/>
+      <c r="J6" s="83"/>
+      <c r="K6" s="84"/>
+    </row>
+    <row r="7" s="60" customFormat="1" ht="30" customHeight="1" spans="1:11">
+      <c r="A7" s="85" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="73" t="s">
+      <c r="B7" s="66" t="s">
         <v>104</v>
       </c>
-      <c r="C7" s="74" t="s">
+      <c r="C7" s="67" t="s">
         <v>42</v>
       </c>
-      <c r="D7" s="74" t="s">
+      <c r="D7" s="67" t="s">
         <v>105</v>
       </c>
-      <c r="E7" s="74" t="s">
+      <c r="E7" s="67" t="s">
         <v>106</v>
       </c>
-      <c r="F7" s="74" t="s">
+      <c r="F7" s="67" t="s">
         <v>40</v>
       </c>
-      <c r="G7" s="74" t="s">
+      <c r="G7" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="H7" s="74" t="s">
+      <c r="H7" s="67" t="s">
         <v>107</v>
       </c>
-      <c r="I7" s="9" t="s">
+      <c r="I7" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="J7" s="9" t="s">
+      <c r="J7" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="K7" s="31" t="s">
+      <c r="K7" s="11" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:11">
-      <c r="A8" s="96" t="s">
+      <c r="A8" s="86" t="s">
         <v>111</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="F8" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="G8" s="14">
-        <v>1</v>
-      </c>
-      <c r="H8" s="32" t="s">
+      <c r="G8" s="16">
+        <v>1</v>
+      </c>
+      <c r="H8" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="I8" s="84">
-        <v>1</v>
-      </c>
-      <c r="J8" s="84">
+      <c r="I8" s="69">
+        <v>1</v>
+      </c>
+      <c r="J8" s="69">
         <v>167</v>
       </c>
-      <c r="K8" s="99">
+      <c r="K8" s="87">
         <v>200</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:11">
-      <c r="A9" s="8"/>
-      <c r="B9" s="16" t="s">
+      <c r="A9" s="9"/>
+      <c r="B9" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="F9" s="18" t="s">
+      <c r="F9" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="G9" s="18">
-        <v>1</v>
-      </c>
-      <c r="H9" s="34" t="s">
+      <c r="G9" s="22">
+        <v>1</v>
+      </c>
+      <c r="H9" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="I9" s="100">
-        <v>1</v>
-      </c>
-      <c r="J9" s="100">
+      <c r="I9" s="88">
+        <v>1</v>
+      </c>
+      <c r="J9" s="88">
         <v>167</v>
       </c>
-      <c r="K9" s="101">
+      <c r="K9" s="89">
         <v>200</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:11">
-      <c r="A10" s="8"/>
-      <c r="B10" s="13" t="s">
+      <c r="A10" s="9"/>
+      <c r="B10" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="F10" s="14" t="s">
+      <c r="F10" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="G10" s="14">
-        <v>1</v>
-      </c>
-      <c r="H10" s="32" t="s">
+      <c r="G10" s="16">
+        <v>1</v>
+      </c>
+      <c r="H10" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="I10" s="84">
-        <v>1</v>
-      </c>
-      <c r="J10" s="84">
+      <c r="I10" s="69">
+        <v>1</v>
+      </c>
+      <c r="J10" s="69">
         <v>167</v>
       </c>
-      <c r="K10" s="99">
+      <c r="K10" s="87">
         <v>200</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:11">
-      <c r="A11" s="8"/>
-      <c r="B11" s="16" t="s">
+      <c r="A11" s="9"/>
+      <c r="B11" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="D11" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="E11" s="17" t="s">
+      <c r="E11" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="F11" s="18" t="s">
+      <c r="F11" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="G11" s="18">
-        <v>1</v>
-      </c>
-      <c r="H11" s="34" t="s">
+      <c r="G11" s="22">
+        <v>1</v>
+      </c>
+      <c r="H11" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="I11" s="100">
-        <v>1</v>
-      </c>
-      <c r="J11" s="100">
+      <c r="I11" s="88">
+        <v>1</v>
+      </c>
+      <c r="J11" s="88">
         <v>167</v>
       </c>
-      <c r="K11" s="101">
+      <c r="K11" s="89">
         <v>200</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:11">
-      <c r="A12" s="8"/>
-      <c r="B12" s="13" t="s">
+      <c r="A12" s="9"/>
+      <c r="B12" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="F12" s="14" t="s">
+      <c r="F12" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="G12" s="14">
-        <v>1</v>
-      </c>
-      <c r="H12" s="32" t="s">
+      <c r="G12" s="16">
+        <v>1</v>
+      </c>
+      <c r="H12" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="I12" s="84">
-        <v>1</v>
-      </c>
-      <c r="J12" s="84">
+      <c r="I12" s="69">
+        <v>1</v>
+      </c>
+      <c r="J12" s="69">
         <v>167</v>
       </c>
-      <c r="K12" s="99">
+      <c r="K12" s="87">
         <v>200</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:11">
-      <c r="A13" s="8"/>
-      <c r="B13" s="16" t="s">
+      <c r="A13" s="9"/>
+      <c r="B13" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="C13" s="17" t="s">
+      <c r="C13" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="D13" s="17" t="s">
+      <c r="D13" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="E13" s="17" t="s">
+      <c r="E13" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="F13" s="18" t="s">
+      <c r="F13" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="G13" s="18">
-        <v>1</v>
-      </c>
-      <c r="H13" s="34" t="s">
+      <c r="G13" s="22">
+        <v>1</v>
+      </c>
+      <c r="H13" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="I13" s="100">
-        <v>1</v>
-      </c>
-      <c r="J13" s="100">
+      <c r="I13" s="88">
+        <v>1</v>
+      </c>
+      <c r="J13" s="88">
         <v>167</v>
       </c>
-      <c r="K13" s="101">
+      <c r="K13" s="89">
         <v>200</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:11">
-      <c r="A14" s="8"/>
-      <c r="B14" s="13" t="s">
+      <c r="A14" s="9"/>
+      <c r="B14" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E14" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="F14" s="14" t="s">
+      <c r="F14" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="G14" s="14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="32" t="s">
+      <c r="G14" s="16">
+        <v>1</v>
+      </c>
+      <c r="H14" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="I14" s="84">
-        <v>1</v>
-      </c>
-      <c r="J14" s="84">
+      <c r="I14" s="69">
+        <v>1</v>
+      </c>
+      <c r="J14" s="69">
         <v>167</v>
       </c>
-      <c r="K14" s="99">
+      <c r="K14" s="87">
         <v>200</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:11">
-      <c r="A15" s="8"/>
-      <c r="B15" s="16" t="s">
+      <c r="A15" s="9"/>
+      <c r="B15" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="D15" s="17" t="s">
+      <c r="D15" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="E15" s="17" t="s">
+      <c r="E15" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="F15" s="18" t="s">
+      <c r="F15" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="G15" s="18">
-        <v>1</v>
-      </c>
-      <c r="H15" s="34" t="s">
+      <c r="G15" s="22">
+        <v>1</v>
+      </c>
+      <c r="H15" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="I15" s="100">
-        <v>1</v>
-      </c>
-      <c r="J15" s="100">
+      <c r="I15" s="88">
+        <v>1</v>
+      </c>
+      <c r="J15" s="88">
         <v>167</v>
       </c>
-      <c r="K15" s="101">
+      <c r="K15" s="89">
         <v>200</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:11">
-      <c r="A16" s="8"/>
-      <c r="B16" s="13" t="s">
+      <c r="A16" s="9"/>
+      <c r="B16" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="E16" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="F16" s="14" t="s">
+      <c r="F16" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="G16" s="14">
-        <v>1</v>
-      </c>
-      <c r="H16" s="32" t="s">
+      <c r="G16" s="16">
+        <v>1</v>
+      </c>
+      <c r="H16" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="I16" s="84">
-        <v>1</v>
-      </c>
-      <c r="J16" s="84">
+      <c r="I16" s="69">
+        <v>1</v>
+      </c>
+      <c r="J16" s="69">
         <v>167</v>
       </c>
-      <c r="K16" s="99">
+      <c r="K16" s="87">
         <v>200</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:11">
-      <c r="A17" s="97"/>
-      <c r="B17" s="78"/>
-      <c r="C17" s="78"/>
-      <c r="D17" s="78"/>
-      <c r="E17" s="78"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="79">
+      <c r="A17" s="90"/>
+      <c r="B17" s="73"/>
+      <c r="C17" s="73"/>
+      <c r="D17" s="73"/>
+      <c r="E17" s="73"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="74">
         <f>SUM(G8:G16)</f>
         <v>9</v>
       </c>
-      <c r="H17" s="79"/>
-      <c r="I17" s="87">
+      <c r="H17" s="74"/>
+      <c r="I17" s="75">
         <f>SUM(I8:I16)</f>
         <v>9</v>
       </c>
-      <c r="J17" s="87">
+      <c r="J17" s="75">
         <f>SUM(J8:J16)</f>
         <v>1503</v>
       </c>
-      <c r="K17" s="88">
+      <c r="K17" s="76">
         <f>SUM(K8:K16)</f>
         <v>1800</v>
       </c>
     </row>
-    <row r="18" s="66" customFormat="1" ht="30" customHeight="1" spans="1:11">
-      <c r="A18" s="80" t="s">
+    <row r="18" s="59" customFormat="1" ht="30" customHeight="1" spans="1:11">
+      <c r="A18" s="77" t="s">
         <v>121</v>
       </c>
-      <c r="B18" s="82"/>
-      <c r="C18" s="82"/>
-      <c r="D18" s="82"/>
-      <c r="E18" s="82"/>
-      <c r="F18" s="82"/>
-      <c r="G18" s="82"/>
-      <c r="H18" s="82"/>
-      <c r="I18" s="82"/>
-      <c r="J18" s="82"/>
-      <c r="K18" s="90"/>
+      <c r="B18" s="78"/>
+      <c r="C18" s="78"/>
+      <c r="D18" s="78"/>
+      <c r="E18" s="78"/>
+      <c r="F18" s="78"/>
+      <c r="G18" s="78"/>
+      <c r="H18" s="78"/>
+      <c r="I18" s="78"/>
+      <c r="J18" s="78"/>
+      <c r="K18" s="79"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4527,7 +4708,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A5:L17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="10.625" customWidth="1"/>
     <col min="2" max="2" width="15.625" customWidth="1"/>
@@ -4538,443 +4719,443 @@
     <col min="8" max="12" width="15.625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" s="66" customFormat="1" ht="30" customHeight="1" spans="1:12">
-      <c r="A5" s="68" t="s">
+    <row r="5" s="59" customFormat="1" ht="30" customHeight="1" spans="1:12">
+      <c r="A5" s="61" t="s">
         <v>122</v>
       </c>
-      <c r="B5" s="69"/>
-      <c r="C5" s="70"/>
-      <c r="D5" s="70"/>
-      <c r="E5" s="70"/>
-      <c r="F5" s="70"/>
-      <c r="G5" s="70"/>
-      <c r="H5" s="71"/>
-      <c r="I5" s="71"/>
-      <c r="J5" s="71"/>
-      <c r="K5" s="71"/>
-      <c r="L5" s="83"/>
-    </row>
-    <row r="6" s="67" customFormat="1" ht="30" customHeight="1" spans="1:12">
-      <c r="A6" s="72" t="s">
+      <c r="B5" s="62"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="63"/>
+      <c r="I5" s="63"/>
+      <c r="J5" s="63"/>
+      <c r="K5" s="63"/>
+      <c r="L5" s="64"/>
+    </row>
+    <row r="6" s="60" customFormat="1" ht="30" customHeight="1" spans="1:12">
+      <c r="A6" s="65" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="73" t="s">
+      <c r="B6" s="66" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="74" t="s">
+      <c r="C6" s="67" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="74" t="s">
+      <c r="D6" s="67" t="s">
         <v>105</v>
       </c>
-      <c r="E6" s="74" t="s">
+      <c r="E6" s="67" t="s">
         <v>106</v>
       </c>
-      <c r="F6" s="74" t="s">
+      <c r="F6" s="67" t="s">
         <v>40</v>
       </c>
-      <c r="G6" s="74" t="s">
+      <c r="G6" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="H6" s="74" t="s">
+      <c r="H6" s="67" t="s">
         <v>107</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="I6" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="J6" s="9" t="s">
+      <c r="J6" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="K6" s="9" t="s">
+      <c r="K6" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="L6" s="31" t="s">
+      <c r="L6" s="11" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:12">
-      <c r="A7" s="75">
-        <v>1</v>
-      </c>
-      <c r="B7" s="13" t="s">
+      <c r="A7" s="68">
+        <v>1</v>
+      </c>
+      <c r="B7" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="14">
         <v>191021000022</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="G7" s="14">
-        <v>1</v>
-      </c>
-      <c r="H7" s="32" t="s">
+      <c r="G7" s="16">
+        <v>1</v>
+      </c>
+      <c r="H7" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="I7" s="84">
-        <v>1</v>
-      </c>
-      <c r="J7" s="84">
+      <c r="I7" s="69">
+        <v>1</v>
+      </c>
+      <c r="J7" s="69">
         <v>167</v>
       </c>
-      <c r="K7" s="85">
+      <c r="K7" s="70">
         <v>200</v>
       </c>
-      <c r="L7" s="86" t="s">
+      <c r="L7" s="71" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:12">
-      <c r="A8" s="75">
+      <c r="A8" s="68">
         <v>2</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="14">
         <v>191021000022</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="F8" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="G8" s="14">
-        <v>1</v>
-      </c>
-      <c r="H8" s="32" t="s">
+      <c r="G8" s="16">
+        <v>1</v>
+      </c>
+      <c r="H8" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="I8" s="84">
-        <v>1</v>
-      </c>
-      <c r="J8" s="84">
+      <c r="I8" s="69">
+        <v>1</v>
+      </c>
+      <c r="J8" s="69">
         <v>167</v>
       </c>
-      <c r="K8" s="85">
+      <c r="K8" s="70">
         <v>200</v>
       </c>
-      <c r="L8" s="86" t="s">
+      <c r="L8" s="71" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:12">
-      <c r="A9" s="75">
+      <c r="A9" s="68">
         <v>3</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="14">
         <v>191021000022</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="G9" s="14">
-        <v>1</v>
-      </c>
-      <c r="H9" s="32" t="s">
+      <c r="G9" s="16">
+        <v>1</v>
+      </c>
+      <c r="H9" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="I9" s="84">
-        <v>1</v>
-      </c>
-      <c r="J9" s="84">
+      <c r="I9" s="69">
+        <v>1</v>
+      </c>
+      <c r="J9" s="69">
         <v>167</v>
       </c>
-      <c r="K9" s="85">
+      <c r="K9" s="70">
         <v>200</v>
       </c>
-      <c r="L9" s="86" t="s">
+      <c r="L9" s="71" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:12">
-      <c r="A10" s="75">
+      <c r="A10" s="68">
         <v>4</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="14">
         <v>191021000022</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="F10" s="14" t="s">
+      <c r="F10" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="G10" s="14">
-        <v>1</v>
-      </c>
-      <c r="H10" s="32" t="s">
+      <c r="G10" s="16">
+        <v>1</v>
+      </c>
+      <c r="H10" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="I10" s="84">
-        <v>1</v>
-      </c>
-      <c r="J10" s="84">
+      <c r="I10" s="69">
+        <v>1</v>
+      </c>
+      <c r="J10" s="69">
         <v>167</v>
       </c>
-      <c r="K10" s="85">
+      <c r="K10" s="70">
         <v>200</v>
       </c>
-      <c r="L10" s="86" t="s">
+      <c r="L10" s="71" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:12">
-      <c r="A11" s="75">
+      <c r="A11" s="68">
         <v>5</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="14">
         <v>191021000022</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="E11" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="F11" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="G11" s="14">
-        <v>1</v>
-      </c>
-      <c r="H11" s="32" t="s">
+      <c r="G11" s="16">
+        <v>1</v>
+      </c>
+      <c r="H11" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="I11" s="84">
-        <v>1</v>
-      </c>
-      <c r="J11" s="84">
+      <c r="I11" s="69">
+        <v>1</v>
+      </c>
+      <c r="J11" s="69">
         <v>167</v>
       </c>
-      <c r="K11" s="85">
+      <c r="K11" s="70">
         <v>200</v>
       </c>
-      <c r="L11" s="86" t="s">
+      <c r="L11" s="71" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:12">
-      <c r="A12" s="75">
+      <c r="A12" s="68">
         <v>6</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="14">
         <v>191021000022</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="F12" s="14" t="s">
+      <c r="F12" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="G12" s="14">
-        <v>1</v>
-      </c>
-      <c r="H12" s="32" t="s">
+      <c r="G12" s="16">
+        <v>1</v>
+      </c>
+      <c r="H12" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="I12" s="84">
-        <v>1</v>
-      </c>
-      <c r="J12" s="84">
+      <c r="I12" s="69">
+        <v>1</v>
+      </c>
+      <c r="J12" s="69">
         <v>167</v>
       </c>
-      <c r="K12" s="85">
+      <c r="K12" s="70">
         <v>200</v>
       </c>
-      <c r="L12" s="86" t="s">
+      <c r="L12" s="71" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:12">
-      <c r="A13" s="75">
+      <c r="A13" s="68">
         <v>7</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="14">
         <v>191021000022</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="F13" s="14" t="s">
+      <c r="F13" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="G13" s="14">
-        <v>1</v>
-      </c>
-      <c r="H13" s="32" t="s">
+      <c r="G13" s="16">
+        <v>1</v>
+      </c>
+      <c r="H13" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="I13" s="84">
-        <v>1</v>
-      </c>
-      <c r="J13" s="84">
+      <c r="I13" s="69">
+        <v>1</v>
+      </c>
+      <c r="J13" s="69">
         <v>167</v>
       </c>
-      <c r="K13" s="85">
+      <c r="K13" s="70">
         <v>200</v>
       </c>
-      <c r="L13" s="86" t="s">
+      <c r="L13" s="71" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:12">
-      <c r="A14" s="75">
+      <c r="A14" s="68">
         <v>8</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="14">
         <v>191021000022</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E14" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="F14" s="14" t="s">
+      <c r="F14" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="G14" s="14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="32" t="s">
+      <c r="G14" s="16">
+        <v>1</v>
+      </c>
+      <c r="H14" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="I14" s="84">
-        <v>1</v>
-      </c>
-      <c r="J14" s="84">
+      <c r="I14" s="69">
+        <v>1</v>
+      </c>
+      <c r="J14" s="69">
         <v>167</v>
       </c>
-      <c r="K14" s="85">
+      <c r="K14" s="70">
         <v>200</v>
       </c>
-      <c r="L14" s="86" t="s">
+      <c r="L14" s="71" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:12">
-      <c r="A15" s="75">
+      <c r="A15" s="68">
         <v>9</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="14">
         <v>191021000022</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="E15" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="F15" s="14" t="s">
+      <c r="F15" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="G15" s="14">
-        <v>1</v>
-      </c>
-      <c r="H15" s="32" t="s">
+      <c r="G15" s="16">
+        <v>1</v>
+      </c>
+      <c r="H15" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="I15" s="84">
-        <v>1</v>
-      </c>
-      <c r="J15" s="84">
+      <c r="I15" s="69">
+        <v>1</v>
+      </c>
+      <c r="J15" s="69">
         <v>167</v>
       </c>
-      <c r="K15" s="85">
+      <c r="K15" s="70">
         <v>200</v>
       </c>
-      <c r="L15" s="86" t="s">
+      <c r="L15" s="71" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:12">
-      <c r="A16" s="76"/>
-      <c r="B16" s="77"/>
-      <c r="C16" s="78"/>
-      <c r="D16" s="78"/>
-      <c r="E16" s="78"/>
-      <c r="F16" s="18"/>
-      <c r="G16" s="79">
+      <c r="A16" s="72"/>
+      <c r="B16" s="73"/>
+      <c r="C16" s="73"/>
+      <c r="D16" s="73"/>
+      <c r="E16" s="73"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="74">
         <f t="shared" ref="G16:K16" si="0">SUM(G7:G15)</f>
         <v>9</v>
       </c>
-      <c r="H16" s="79"/>
-      <c r="I16" s="87">
+      <c r="H16" s="74"/>
+      <c r="I16" s="75">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="J16" s="87">
+      <c r="J16" s="75">
         <f t="shared" si="0"/>
         <v>1503</v>
       </c>
-      <c r="K16" s="87">
+      <c r="K16" s="75">
         <f t="shared" si="0"/>
         <v>1800</v>
       </c>
-      <c r="L16" s="88"/>
-    </row>
-    <row r="17" s="66" customFormat="1" ht="30" customHeight="1" spans="1:12">
-      <c r="A17" s="80" t="s">
+      <c r="L16" s="76"/>
+    </row>
+    <row r="17" s="59" customFormat="1" ht="30" customHeight="1" spans="1:12">
+      <c r="A17" s="77" t="s">
         <v>125</v>
       </c>
-      <c r="B17" s="81"/>
-      <c r="C17" s="82"/>
-      <c r="D17" s="82"/>
-      <c r="E17" s="82"/>
-      <c r="F17" s="82"/>
-      <c r="G17" s="82"/>
-      <c r="H17" s="82"/>
-      <c r="I17" s="82"/>
-      <c r="J17" s="82"/>
-      <c r="K17" s="89"/>
-      <c r="L17" s="90"/>
+      <c r="B17" s="78"/>
+      <c r="C17" s="78"/>
+      <c r="D17" s="78"/>
+      <c r="E17" s="78"/>
+      <c r="F17" s="78"/>
+      <c r="G17" s="78"/>
+      <c r="H17" s="78"/>
+      <c r="I17" s="78"/>
+      <c r="J17" s="78"/>
+      <c r="K17" s="78"/>
+      <c r="L17" s="79"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4989,185 +5170,169 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A2:F13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="2" width="10.625" style="41" customWidth="1"/>
-    <col min="3" max="3" width="50.625" style="42" customWidth="1"/>
-    <col min="4" max="5" width="10.625" style="41" customWidth="1"/>
-    <col min="6" max="6" width="50.625" style="42" customWidth="1"/>
-    <col min="7" max="16358" width="9" style="41"/>
-    <col min="16362" max="16374" width="9" style="41"/>
+    <col min="1" max="2" width="10.625" style="35" customWidth="1"/>
+    <col min="3" max="3" width="50.625" style="36" customWidth="1"/>
+    <col min="4" max="5" width="10.625" style="35" customWidth="1"/>
+    <col min="6" max="6" width="50.625" style="36" customWidth="1"/>
+    <col min="7" max="16358" width="9" style="35"/>
+    <col min="16362" max="16374" width="9" style="35"/>
   </cols>
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="1:6">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="37" t="s">
         <v>126</v>
       </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="45"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="39"/>
     </row>
     <row r="3" customFormat="1" ht="30" customHeight="1" spans="1:6">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="47"/>
-      <c r="C3" s="48" t="s">
+      <c r="B3" s="41"/>
+      <c r="C3" s="42" t="s">
         <v>127</v>
       </c>
-      <c r="D3" s="49" t="s">
+      <c r="D3" s="43" t="s">
         <v>128</v>
       </c>
-      <c r="E3" s="50" t="s">
+      <c r="E3" s="44" t="s">
         <v>129</v>
       </c>
-      <c r="F3" s="51" t="s">
+      <c r="F3" s="45" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="4" customFormat="1" ht="30" customHeight="1" spans="1:6">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="46"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="44" t="s">
         <v>131</v>
       </c>
-      <c r="B4" s="47"/>
-      <c r="C4" s="53" t="s">
+      <c r="F4" s="48" t="s">
         <v>132</v>
       </c>
-      <c r="D4" s="49"/>
-      <c r="E4" s="50" t="s">
+    </row>
+    <row r="5" s="34" customFormat="1" ht="30" customHeight="1" spans="1:6">
+      <c r="A5" s="46" t="s">
         <v>133</v>
       </c>
-      <c r="F4" s="54" t="s">
+      <c r="B5" s="41"/>
+      <c r="C5" s="49" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="5" s="40" customFormat="1" ht="30" customHeight="1" spans="1:6">
-      <c r="A5" s="52" t="s">
+      <c r="D5" s="43"/>
+      <c r="E5" s="44" t="s">
         <v>135</v>
       </c>
-      <c r="B5" s="47"/>
-      <c r="C5" s="55" t="s">
+      <c r="F5" s="45" t="s">
         <v>136</v>
       </c>
-      <c r="D5" s="49"/>
-      <c r="E5" s="50" t="s">
+    </row>
+    <row r="6" s="34" customFormat="1" ht="2" customHeight="1" spans="1:6">
+      <c r="A6" s="46"/>
+      <c r="B6" s="41"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="50"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="52"/>
+    </row>
+    <row r="7" s="34" customFormat="1" ht="30" customHeight="1" spans="1:6">
+      <c r="A7" s="46"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="43" t="s">
         <v>137</v>
       </c>
-      <c r="F5" s="51" t="s">
+      <c r="E7" s="43"/>
+      <c r="F7" s="45" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="6" s="40" customFormat="1" ht="2" customHeight="1" spans="1:6">
-      <c r="A6" s="52"/>
-      <c r="B6" s="47"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="56"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="58"/>
-    </row>
-    <row r="7" s="40" customFormat="1" ht="30" customHeight="1" spans="1:6">
-      <c r="A7" s="52" t="s">
+    <row r="8" s="34" customFormat="1" ht="30" customHeight="1" spans="1:6">
+      <c r="A8" s="46"/>
+      <c r="B8" s="41"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="53"/>
+    </row>
+    <row r="9" s="34" customFormat="1" ht="30" customHeight="1" spans="1:6">
+      <c r="A9" s="46" t="s">
         <v>139</v>
       </c>
-      <c r="B7" s="47"/>
-      <c r="C7" s="48" t="s">
+      <c r="B9" s="41"/>
+      <c r="C9" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="D7" s="49" t="s">
+      <c r="D9" s="43" t="s">
         <v>141</v>
       </c>
-      <c r="E7" s="49"/>
-      <c r="F7" s="51" t="s">
+      <c r="E9" s="43"/>
+      <c r="F9" s="45" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="8" s="40" customFormat="1" ht="30" customHeight="1" spans="1:6">
-      <c r="A8" s="52" t="s">
-        <v>44</v>
-      </c>
-      <c r="B8" s="47"/>
-      <c r="C8" s="48">
-        <v>50</v>
-      </c>
-      <c r="D8" s="49" t="s">
+    <row r="10" s="34" customFormat="1" ht="30" customHeight="1" spans="1:6">
+      <c r="A10" s="46" t="s">
         <v>143</v>
       </c>
-      <c r="E8" s="49"/>
-      <c r="F8" s="59" t="s">
+      <c r="B10" s="41"/>
+      <c r="C10" s="54" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="9" s="40" customFormat="1" ht="30" customHeight="1" spans="1:6">
-      <c r="A9" s="52" t="s">
+      <c r="D10" s="43" t="s">
         <v>145</v>
       </c>
-      <c r="B9" s="47"/>
-      <c r="C9" s="60" t="s">
+      <c r="E10" s="43"/>
+      <c r="F10" s="45" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="11" s="34" customFormat="1" ht="30" customHeight="1" spans="1:6">
+      <c r="A11" s="46" t="s">
         <v>146</v>
       </c>
-      <c r="D9" s="49" t="s">
+      <c r="B11" s="43"/>
+      <c r="C11" s="55" t="s">
         <v>147</v>
       </c>
-      <c r="E9" s="49"/>
-      <c r="F9" s="51" t="s">
+      <c r="D11" s="43" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="10" s="40" customFormat="1" ht="30" customHeight="1" spans="1:6">
-      <c r="A10" s="52" t="s">
+      <c r="E11" s="43"/>
+      <c r="F11" s="45" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="12" s="34" customFormat="1" ht="30" customHeight="1" spans="1:6">
+      <c r="A12" s="46"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="49"/>
+      <c r="D12" s="43" t="s">
         <v>149</v>
       </c>
-      <c r="B10" s="47"/>
-      <c r="C10" s="60" t="s">
+      <c r="E12" s="43"/>
+      <c r="F12" s="45" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="13" s="34" customFormat="1" ht="30" customHeight="1" spans="1:6">
+      <c r="A13" s="56" t="s">
         <v>150</v>
       </c>
-      <c r="D10" s="49" t="s">
-        <v>151</v>
-      </c>
-      <c r="E10" s="49"/>
-      <c r="F10" s="51" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="11" s="40" customFormat="1" ht="30" customHeight="1" spans="1:6">
-      <c r="A11" s="61" t="s">
-        <v>152</v>
-      </c>
-      <c r="B11" s="49"/>
-      <c r="C11" s="62" t="s">
-        <v>144</v>
-      </c>
-      <c r="D11" s="49" t="s">
-        <v>153</v>
-      </c>
-      <c r="E11" s="49"/>
-      <c r="F11" s="51" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="12" s="40" customFormat="1" ht="30" customHeight="1" spans="1:6">
-      <c r="A12" s="61"/>
-      <c r="B12" s="49"/>
-      <c r="C12" s="55"/>
-      <c r="D12" s="49" t="s">
-        <v>154</v>
-      </c>
-      <c r="E12" s="49"/>
-      <c r="F12" s="51" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="13" s="40" customFormat="1" ht="30" customHeight="1" spans="1:6">
-      <c r="A13" s="63" t="s">
-        <v>155</v>
-      </c>
-      <c r="B13" s="64"/>
-      <c r="C13" s="64"/>
-      <c r="D13" s="64"/>
-      <c r="E13" s="64"/>
-      <c r="F13" s="65"/>
+      <c r="B13" s="57"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="57"/>
+      <c r="F13" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="19">
@@ -5201,185 +5366,185 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A2:F13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="2" width="10.625" style="41" customWidth="1"/>
-    <col min="3" max="3" width="50.625" style="42" customWidth="1"/>
-    <col min="4" max="5" width="10.625" style="41" customWidth="1"/>
-    <col min="6" max="6" width="50.625" style="42" customWidth="1"/>
-    <col min="7" max="16358" width="9" style="41"/>
-    <col min="16362" max="16374" width="9" style="41"/>
+    <col min="1" max="2" width="10.625" style="35" customWidth="1"/>
+    <col min="3" max="3" width="50.625" style="36" customWidth="1"/>
+    <col min="4" max="5" width="10.625" style="35" customWidth="1"/>
+    <col min="6" max="6" width="50.625" style="36" customWidth="1"/>
+    <col min="7" max="16358" width="9" style="35"/>
+    <col min="16362" max="16374" width="9" style="35"/>
   </cols>
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="1:6">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="37" t="s">
         <v>126</v>
       </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="45"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="39"/>
     </row>
     <row r="3" customFormat="1" ht="30" customHeight="1" spans="1:6">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="47"/>
-      <c r="C3" s="48" t="s">
+      <c r="B3" s="41"/>
+      <c r="C3" s="42" t="s">
         <v>127</v>
       </c>
-      <c r="D3" s="49" t="s">
+      <c r="D3" s="43" t="s">
         <v>128</v>
       </c>
-      <c r="E3" s="50" t="s">
+      <c r="E3" s="44" t="s">
         <v>129</v>
       </c>
-      <c r="F3" s="51" t="s">
+      <c r="F3" s="45" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="4" customFormat="1" ht="30" customHeight="1" spans="1:6">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="46" t="s">
+        <v>151</v>
+      </c>
+      <c r="B4" s="41"/>
+      <c r="C4" s="47" t="s">
+        <v>152</v>
+      </c>
+      <c r="D4" s="43"/>
+      <c r="E4" s="44" t="s">
         <v>131</v>
       </c>
-      <c r="B4" s="47"/>
-      <c r="C4" s="53" t="s">
+      <c r="F4" s="48" t="s">
         <v>132</v>
       </c>
-      <c r="D4" s="49"/>
-      <c r="E4" s="50" t="s">
+    </row>
+    <row r="5" s="34" customFormat="1" ht="30" customHeight="1" spans="1:6">
+      <c r="A5" s="46" t="s">
         <v>133</v>
       </c>
-      <c r="F4" s="54" t="s">
+      <c r="B5" s="41"/>
+      <c r="C5" s="49" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="5" s="40" customFormat="1" ht="30" customHeight="1" spans="1:6">
-      <c r="A5" s="52" t="s">
+      <c r="D5" s="43"/>
+      <c r="E5" s="44" t="s">
         <v>135</v>
       </c>
-      <c r="B5" s="47"/>
-      <c r="C5" s="55" t="s">
+      <c r="F5" s="45" t="s">
         <v>136</v>
       </c>
-      <c r="D5" s="49"/>
-      <c r="E5" s="50" t="s">
+    </row>
+    <row r="6" s="34" customFormat="1" ht="2" customHeight="1" spans="1:6">
+      <c r="A6" s="46"/>
+      <c r="B6" s="41"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="50"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="52"/>
+    </row>
+    <row r="7" s="34" customFormat="1" ht="30" customHeight="1" spans="1:6">
+      <c r="A7" s="46" t="s">
+        <v>153</v>
+      </c>
+      <c r="B7" s="41"/>
+      <c r="C7" s="42" t="s">
+        <v>154</v>
+      </c>
+      <c r="D7" s="43" t="s">
         <v>137</v>
       </c>
-      <c r="F5" s="51" t="s">
+      <c r="E7" s="43"/>
+      <c r="F7" s="45" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="6" s="40" customFormat="1" ht="2" customHeight="1" spans="1:6">
-      <c r="A6" s="52"/>
-      <c r="B6" s="47"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="56"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="58"/>
-    </row>
-    <row r="7" s="40" customFormat="1" ht="30" customHeight="1" spans="1:6">
-      <c r="A7" s="52" t="s">
+    <row r="8" s="34" customFormat="1" ht="30" customHeight="1" spans="1:6">
+      <c r="A8" s="46" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" s="41"/>
+      <c r="C8" s="42">
+        <v>50</v>
+      </c>
+      <c r="D8" s="43" t="s">
+        <v>155</v>
+      </c>
+      <c r="E8" s="43"/>
+      <c r="F8" s="53" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="9" s="34" customFormat="1" ht="30" customHeight="1" spans="1:6">
+      <c r="A9" s="46" t="s">
         <v>139</v>
       </c>
-      <c r="B7" s="47"/>
-      <c r="C7" s="48" t="s">
+      <c r="B9" s="41"/>
+      <c r="C9" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="D7" s="49" t="s">
+      <c r="D9" s="43" t="s">
         <v>141</v>
       </c>
-      <c r="E7" s="49"/>
-      <c r="F7" s="51" t="s">
+      <c r="E9" s="43"/>
+      <c r="F9" s="45" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="8" s="40" customFormat="1" ht="30" customHeight="1" spans="1:6">
-      <c r="A8" s="52" t="s">
-        <v>44</v>
-      </c>
-      <c r="B8" s="47"/>
-      <c r="C8" s="48">
-        <v>50</v>
-      </c>
-      <c r="D8" s="49" t="s">
+    <row r="10" s="34" customFormat="1" ht="30" customHeight="1" spans="1:6">
+      <c r="A10" s="46" t="s">
         <v>143</v>
       </c>
-      <c r="E8" s="49"/>
-      <c r="F8" s="59" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="9" s="40" customFormat="1" ht="30" customHeight="1" spans="1:6">
-      <c r="A9" s="52" t="s">
+      <c r="B10" s="41"/>
+      <c r="C10" s="54" t="s">
+        <v>157</v>
+      </c>
+      <c r="D10" s="43" t="s">
         <v>145</v>
       </c>
-      <c r="B9" s="47"/>
-      <c r="C9" s="60" t="s">
+      <c r="E10" s="43"/>
+      <c r="F10" s="45" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="11" s="34" customFormat="1" ht="30" customHeight="1" spans="1:6">
+      <c r="A11" s="46" t="s">
         <v>146</v>
       </c>
-      <c r="D9" s="49" t="s">
+      <c r="B11" s="43"/>
+      <c r="C11" s="55" t="s">
         <v>147</v>
       </c>
-      <c r="E9" s="49"/>
-      <c r="F9" s="51" t="s">
+      <c r="D11" s="43" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="10" s="40" customFormat="1" ht="30" customHeight="1" spans="1:6">
-      <c r="A10" s="52" t="s">
+      <c r="E11" s="43"/>
+      <c r="F11" s="45" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="12" s="34" customFormat="1" ht="30" customHeight="1" spans="1:6">
+      <c r="A12" s="46"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="49"/>
+      <c r="D12" s="43" t="s">
         <v>149</v>
       </c>
-      <c r="B10" s="47"/>
-      <c r="C10" s="60" t="s">
-        <v>157</v>
-      </c>
-      <c r="D10" s="49" t="s">
-        <v>151</v>
-      </c>
-      <c r="E10" s="49"/>
-      <c r="F10" s="51" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="11" s="40" customFormat="1" ht="30" customHeight="1" spans="1:6">
-      <c r="A11" s="61" t="s">
-        <v>152</v>
-      </c>
-      <c r="B11" s="49"/>
-      <c r="C11" s="62" t="s">
-        <v>144</v>
-      </c>
-      <c r="D11" s="49" t="s">
-        <v>153</v>
-      </c>
-      <c r="E11" s="49"/>
-      <c r="F11" s="51" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="12" s="40" customFormat="1" ht="30" customHeight="1" spans="1:6">
-      <c r="A12" s="61"/>
-      <c r="B12" s="49"/>
-      <c r="C12" s="55"/>
-      <c r="D12" s="49" t="s">
-        <v>154</v>
-      </c>
-      <c r="E12" s="49"/>
-      <c r="F12" s="51" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="13" s="40" customFormat="1" ht="30" customHeight="1" spans="1:6">
-      <c r="A13" s="63" t="s">
+      <c r="E12" s="43"/>
+      <c r="F12" s="45" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="13" s="34" customFormat="1" ht="30" customHeight="1" spans="1:6">
+      <c r="A13" s="56" t="s">
         <v>158</v>
       </c>
-      <c r="B13" s="64"/>
-      <c r="C13" s="64"/>
-      <c r="D13" s="64"/>
-      <c r="E13" s="64"/>
-      <c r="F13" s="65"/>
+      <c r="B13" s="57"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="57"/>
+      <c r="F13" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="19">
@@ -5413,7 +5578,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B3:L19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
     <col min="2" max="3" width="15.625" style="4" customWidth="1"/>
@@ -5435,487 +5600,487 @@
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
-      <c r="J3" s="28"/>
-      <c r="K3" s="28"/>
-      <c r="L3" s="29"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="8"/>
     </row>
     <row r="4" s="1" customFormat="1" ht="30" customHeight="1" spans="2:12">
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="J4" s="30" t="s">
+      <c r="J4" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="K4" s="30" t="s">
+      <c r="K4" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="L4" s="31" t="s">
+      <c r="L4" s="11" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="2:12">
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="13" t="s">
         <v>167</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="G5" s="14" t="s">
+      <c r="G5" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="H5" s="13">
-        <v>1</v>
-      </c>
-      <c r="I5" s="32" t="s">
+      <c r="H5" s="15">
+        <v>1</v>
+      </c>
+      <c r="I5" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="J5" s="13">
+      <c r="J5" s="15">
         <v>0.52</v>
       </c>
-      <c r="K5" s="13">
+      <c r="K5" s="15">
         <v>0.52</v>
       </c>
-      <c r="L5" s="33">
+      <c r="L5" s="18">
         <v>0.52</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="2:12">
-      <c r="B6" s="10"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="12" t="s">
+      <c r="B6" s="12"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="H6" s="13">
-        <v>1</v>
-      </c>
-      <c r="I6" s="32" t="s">
+      <c r="H6" s="15">
+        <v>1</v>
+      </c>
+      <c r="I6" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="J6" s="13">
+      <c r="J6" s="15">
         <v>0.92</v>
       </c>
-      <c r="K6" s="13">
+      <c r="K6" s="15">
         <v>0.92</v>
       </c>
-      <c r="L6" s="33">
+      <c r="L6" s="18">
         <v>0.92</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="2:12">
-      <c r="B7" s="10"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="12" t="s">
+      <c r="B7" s="12"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="G7" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="H7" s="13">
-        <v>1</v>
-      </c>
-      <c r="I7" s="32" t="s">
+      <c r="H7" s="15">
+        <v>1</v>
+      </c>
+      <c r="I7" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="J7" s="13">
+      <c r="J7" s="15">
         <v>0.12</v>
       </c>
-      <c r="K7" s="13">
+      <c r="K7" s="15">
         <v>0.12</v>
       </c>
-      <c r="L7" s="33">
+      <c r="L7" s="18">
         <v>0.12</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="2:12">
-      <c r="B8" s="10"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="12" t="s">
+      <c r="B8" s="12"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="F8" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="G8" s="14" t="s">
+      <c r="G8" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="H8" s="13">
-        <v>1</v>
-      </c>
-      <c r="I8" s="32" t="s">
+      <c r="H8" s="15">
+        <v>1</v>
+      </c>
+      <c r="I8" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="J8" s="13">
+      <c r="J8" s="15">
         <v>2.2</v>
       </c>
-      <c r="K8" s="13">
+      <c r="K8" s="15">
         <v>2.2</v>
       </c>
-      <c r="L8" s="33">
+      <c r="L8" s="18">
         <v>2.2</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="2:12">
-      <c r="B9" s="10"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="12" t="s">
+      <c r="B9" s="12"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E9" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="F9" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="G9" s="14" t="s">
+      <c r="G9" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="H9" s="13">
-        <v>1</v>
-      </c>
-      <c r="I9" s="32" t="s">
+      <c r="H9" s="15">
+        <v>1</v>
+      </c>
+      <c r="I9" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="J9" s="13">
+      <c r="J9" s="15">
         <v>7.1</v>
       </c>
-      <c r="K9" s="13">
+      <c r="K9" s="15">
         <v>7.1</v>
       </c>
-      <c r="L9" s="33">
+      <c r="L9" s="18">
         <v>7.1</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="2:12">
-      <c r="B10" s="10"/>
-      <c r="C10" s="16" t="s">
+      <c r="B10" s="12"/>
+      <c r="C10" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="D10" s="21" t="s">
         <v>175</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="E10" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="F10" s="16" t="s">
+      <c r="F10" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="G10" s="18" t="s">
+      <c r="G10" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="H10" s="16">
-        <v>1</v>
-      </c>
-      <c r="I10" s="34" t="s">
+      <c r="H10" s="20">
+        <v>1</v>
+      </c>
+      <c r="I10" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="J10" s="16">
+      <c r="J10" s="20">
         <v>1.14</v>
       </c>
-      <c r="K10" s="16">
+      <c r="K10" s="20">
         <v>1.14</v>
       </c>
-      <c r="L10" s="35">
+      <c r="L10" s="24">
         <v>1.14</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="2:12">
-      <c r="B11" s="10"/>
-      <c r="C11" s="13" t="s">
+      <c r="B11" s="12"/>
+      <c r="C11" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E11" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="F11" s="13" t="s">
+      <c r="F11" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="G11" s="14" t="s">
+      <c r="G11" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="H11" s="13">
-        <v>1</v>
-      </c>
-      <c r="I11" s="32" t="s">
+      <c r="H11" s="15">
+        <v>1</v>
+      </c>
+      <c r="I11" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="J11" s="13">
+      <c r="J11" s="15">
         <v>0.92</v>
       </c>
-      <c r="K11" s="13">
+      <c r="K11" s="15">
         <v>0.92</v>
       </c>
-      <c r="L11" s="33">
+      <c r="L11" s="18">
         <v>0.92</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="2:12">
-      <c r="B12" s="10"/>
-      <c r="C12" s="16" t="s">
+      <c r="B12" s="12"/>
+      <c r="C12" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="D12" s="21" t="s">
         <v>171</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E12" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="F12" s="16" t="s">
+      <c r="F12" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="G12" s="18" t="s">
+      <c r="G12" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="H12" s="16">
-        <v>1</v>
-      </c>
-      <c r="I12" s="34" t="s">
+      <c r="H12" s="20">
+        <v>1</v>
+      </c>
+      <c r="I12" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="J12" s="16">
+      <c r="J12" s="20">
         <v>0.12</v>
       </c>
-      <c r="K12" s="16">
+      <c r="K12" s="20">
         <v>0.12</v>
       </c>
-      <c r="L12" s="35">
+      <c r="L12" s="24">
         <v>0.12</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="2:12">
-      <c r="B13" s="10"/>
-      <c r="C13" s="13" t="s">
+      <c r="B13" s="12"/>
+      <c r="C13" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="E13" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="F13" s="13" t="s">
+      <c r="F13" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="G13" s="14" t="s">
+      <c r="G13" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="H13" s="13">
-        <v>1</v>
-      </c>
-      <c r="I13" s="32" t="s">
+      <c r="H13" s="15">
+        <v>1</v>
+      </c>
+      <c r="I13" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="J13" s="13">
+      <c r="J13" s="15">
         <v>2.2</v>
       </c>
-      <c r="K13" s="13">
+      <c r="K13" s="15">
         <v>2.2</v>
       </c>
-      <c r="L13" s="33">
+      <c r="L13" s="18">
         <v>2.2</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="2:12">
-      <c r="B14" s="10"/>
-      <c r="C14" s="16" t="s">
+      <c r="B14" s="12"/>
+      <c r="C14" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="D14" s="21" t="s">
         <v>173</v>
       </c>
-      <c r="E14" s="16" t="s">
+      <c r="E14" s="20" t="s">
         <v>174</v>
       </c>
-      <c r="F14" s="16" t="s">
+      <c r="F14" s="20" t="s">
         <v>174</v>
       </c>
-      <c r="G14" s="18" t="s">
+      <c r="G14" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="H14" s="16">
-        <v>1</v>
-      </c>
-      <c r="I14" s="34" t="s">
+      <c r="H14" s="20">
+        <v>1</v>
+      </c>
+      <c r="I14" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="J14" s="16">
+      <c r="J14" s="20">
         <v>7.1</v>
       </c>
-      <c r="K14" s="16">
+      <c r="K14" s="20">
         <v>7.1</v>
       </c>
-      <c r="L14" s="35">
+      <c r="L14" s="24">
         <v>7.1</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="2:12">
-      <c r="B15" s="10"/>
-      <c r="C15" s="13" t="s">
+      <c r="B15" s="12"/>
+      <c r="C15" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="E15" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="F15" s="13" t="s">
+      <c r="F15" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="G15" s="14" t="s">
+      <c r="G15" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="H15" s="13">
-        <v>1</v>
-      </c>
-      <c r="I15" s="32" t="s">
+      <c r="H15" s="15">
+        <v>1</v>
+      </c>
+      <c r="I15" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="J15" s="13">
+      <c r="J15" s="15">
         <v>1.1</v>
       </c>
-      <c r="K15" s="13">
+      <c r="K15" s="15">
         <v>1.1</v>
       </c>
-      <c r="L15" s="33">
+      <c r="L15" s="18">
         <v>1.1</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="2:12">
-      <c r="B16" s="10"/>
-      <c r="C16" s="16" t="s">
+      <c r="B16" s="12"/>
+      <c r="C16" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="D16" s="17" t="s">
+      <c r="D16" s="21" t="s">
         <v>177</v>
       </c>
-      <c r="E16" s="16" t="s">
+      <c r="E16" s="20" t="s">
         <v>178</v>
       </c>
-      <c r="F16" s="16" t="s">
+      <c r="F16" s="20" t="s">
         <v>178</v>
       </c>
-      <c r="G16" s="18" t="s">
+      <c r="G16" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="H16" s="16">
-        <v>1</v>
-      </c>
-      <c r="I16" s="34" t="s">
+      <c r="H16" s="20">
+        <v>1</v>
+      </c>
+      <c r="I16" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="J16" s="16">
+      <c r="J16" s="20">
         <v>0.94</v>
       </c>
-      <c r="K16" s="16">
+      <c r="K16" s="20">
         <v>0.94</v>
       </c>
-      <c r="L16" s="35">
+      <c r="L16" s="24">
         <v>0.94</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="2:12">
-      <c r="B17" s="19"/>
-      <c r="C17" s="20"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="22">
+      <c r="B17" s="25"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="26"/>
+      <c r="H17" s="27">
         <f t="shared" ref="H17:L17" si="0">SUM(H5:H16)</f>
         <v>12</v>
       </c>
-      <c r="I17" s="22"/>
-      <c r="J17" s="22">
+      <c r="I17" s="27"/>
+      <c r="J17" s="27">
         <f>SUM(J5:J16)</f>
         <v>24.38</v>
       </c>
-      <c r="K17" s="22">
+      <c r="K17" s="27">
         <f t="shared" si="0"/>
         <v>24.38</v>
       </c>
-      <c r="L17" s="37">
+      <c r="L17" s="28">
         <f t="shared" si="0"/>
         <v>24.38</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" ht="30" customHeight="1" spans="2:12">
-      <c r="B18" s="23" t="s">
+      <c r="B18" s="29" t="s">
         <v>179</v>
       </c>
-      <c r="C18" s="24"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="25"/>
-      <c r="H18" s="25"/>
-      <c r="I18" s="25"/>
-      <c r="J18" s="38"/>
-      <c r="K18" s="38"/>
-      <c r="L18" s="39"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="30"/>
+      <c r="H18" s="30"/>
+      <c r="I18" s="30"/>
+      <c r="J18" s="30"/>
+      <c r="K18" s="30"/>
+      <c r="L18" s="31"/>
     </row>
     <row r="19" spans="2:12">
-      <c r="B19" s="26"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="27"/>
-      <c r="H19" s="27"/>
-      <c r="I19" s="27"/>
-      <c r="J19" s="27"/>
-      <c r="K19" s="27"/>
-      <c r="L19" s="27"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="33"/>
+      <c r="E19" s="33"/>
+      <c r="F19" s="33"/>
+      <c r="G19" s="33"/>
+      <c r="H19" s="33"/>
+      <c r="I19" s="33"/>
+      <c r="J19" s="33"/>
+      <c r="K19" s="33"/>
+      <c r="L19" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -5935,7 +6100,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B3:L19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
     <col min="2" max="3" width="15.625" style="4" customWidth="1"/>
@@ -5957,487 +6122,487 @@
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
-      <c r="J3" s="28"/>
-      <c r="K3" s="28"/>
-      <c r="L3" s="29"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="8"/>
     </row>
     <row r="4" s="1" customFormat="1" ht="30" customHeight="1" spans="2:12">
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="J4" s="30" t="s">
+      <c r="J4" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="K4" s="30" t="s">
+      <c r="K4" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="L4" s="31" t="s">
+      <c r="L4" s="11" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="2:12">
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="13" t="s">
         <v>167</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="G5" s="14" t="s">
+      <c r="G5" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="H5" s="13">
-        <v>1</v>
-      </c>
-      <c r="I5" s="32" t="s">
+      <c r="H5" s="15">
+        <v>1</v>
+      </c>
+      <c r="I5" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="J5" s="13">
+      <c r="J5" s="15">
         <v>0.52</v>
       </c>
-      <c r="K5" s="13">
+      <c r="K5" s="15">
         <v>0.52</v>
       </c>
-      <c r="L5" s="33">
+      <c r="L5" s="18">
         <v>0.52</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="2:12">
-      <c r="B6" s="10"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="12" t="s">
+      <c r="B6" s="12"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="H6" s="13">
-        <v>1</v>
-      </c>
-      <c r="I6" s="32" t="s">
+      <c r="H6" s="15">
+        <v>1</v>
+      </c>
+      <c r="I6" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="J6" s="13">
+      <c r="J6" s="15">
         <v>0.92</v>
       </c>
-      <c r="K6" s="13">
+      <c r="K6" s="15">
         <v>0.92</v>
       </c>
-      <c r="L6" s="33">
+      <c r="L6" s="18">
         <v>0.92</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="2:12">
-      <c r="B7" s="10"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="12" t="s">
+      <c r="B7" s="12"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="G7" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="H7" s="13">
-        <v>1</v>
-      </c>
-      <c r="I7" s="32" t="s">
+      <c r="H7" s="15">
+        <v>1</v>
+      </c>
+      <c r="I7" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="J7" s="13">
+      <c r="J7" s="15">
         <v>0.12</v>
       </c>
-      <c r="K7" s="13">
+      <c r="K7" s="15">
         <v>0.12</v>
       </c>
-      <c r="L7" s="33">
+      <c r="L7" s="18">
         <v>0.12</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="2:12">
-      <c r="B8" s="10"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="12" t="s">
+      <c r="B8" s="12"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="F8" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="G8" s="14" t="s">
+      <c r="G8" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="H8" s="13">
-        <v>1</v>
-      </c>
-      <c r="I8" s="32" t="s">
+      <c r="H8" s="15">
+        <v>1</v>
+      </c>
+      <c r="I8" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="J8" s="13">
+      <c r="J8" s="15">
         <v>2.2</v>
       </c>
-      <c r="K8" s="13">
+      <c r="K8" s="15">
         <v>2.2</v>
       </c>
-      <c r="L8" s="33">
+      <c r="L8" s="18">
         <v>2.2</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="2:12">
-      <c r="B9" s="10"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="12" t="s">
+      <c r="B9" s="12"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E9" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="F9" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="G9" s="14" t="s">
+      <c r="G9" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="H9" s="13">
-        <v>1</v>
-      </c>
-      <c r="I9" s="32" t="s">
+      <c r="H9" s="15">
+        <v>1</v>
+      </c>
+      <c r="I9" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="J9" s="13">
+      <c r="J9" s="15">
         <v>7.1</v>
       </c>
-      <c r="K9" s="13">
+      <c r="K9" s="15">
         <v>7.1</v>
       </c>
-      <c r="L9" s="33">
+      <c r="L9" s="18">
         <v>7.1</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="2:12">
-      <c r="B10" s="10"/>
-      <c r="C10" s="16" t="s">
+      <c r="B10" s="12"/>
+      <c r="C10" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="D10" s="21" t="s">
         <v>175</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="E10" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="F10" s="16" t="s">
+      <c r="F10" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="G10" s="18" t="s">
+      <c r="G10" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="H10" s="16">
-        <v>1</v>
-      </c>
-      <c r="I10" s="34" t="s">
+      <c r="H10" s="20">
+        <v>1</v>
+      </c>
+      <c r="I10" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="J10" s="16">
+      <c r="J10" s="20">
         <v>1.14</v>
       </c>
-      <c r="K10" s="16">
+      <c r="K10" s="20">
         <v>1.14</v>
       </c>
-      <c r="L10" s="35">
+      <c r="L10" s="24">
         <v>1.14</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="2:12">
-      <c r="B11" s="10"/>
-      <c r="C11" s="13" t="s">
+      <c r="B11" s="12"/>
+      <c r="C11" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E11" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="F11" s="13" t="s">
+      <c r="F11" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="G11" s="14" t="s">
+      <c r="G11" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="H11" s="13">
-        <v>1</v>
-      </c>
-      <c r="I11" s="32" t="s">
+      <c r="H11" s="15">
+        <v>1</v>
+      </c>
+      <c r="I11" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="J11" s="13">
+      <c r="J11" s="15">
         <v>0.92</v>
       </c>
-      <c r="K11" s="13">
+      <c r="K11" s="15">
         <v>0.92</v>
       </c>
-      <c r="L11" s="33">
+      <c r="L11" s="18">
         <v>0.92</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="2:12">
-      <c r="B12" s="10"/>
-      <c r="C12" s="16" t="s">
+      <c r="B12" s="12"/>
+      <c r="C12" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="D12" s="21" t="s">
         <v>171</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E12" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="F12" s="16" t="s">
+      <c r="F12" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="G12" s="18" t="s">
+      <c r="G12" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="H12" s="16">
-        <v>1</v>
-      </c>
-      <c r="I12" s="34" t="s">
+      <c r="H12" s="20">
+        <v>1</v>
+      </c>
+      <c r="I12" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="J12" s="16">
+      <c r="J12" s="20">
         <v>0.12</v>
       </c>
-      <c r="K12" s="16">
+      <c r="K12" s="20">
         <v>0.12</v>
       </c>
-      <c r="L12" s="35">
+      <c r="L12" s="24">
         <v>0.12</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="2:12">
-      <c r="B13" s="10"/>
-      <c r="C13" s="13" t="s">
+      <c r="B13" s="12"/>
+      <c r="C13" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="E13" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="F13" s="13" t="s">
+      <c r="F13" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="G13" s="14" t="s">
+      <c r="G13" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="H13" s="13">
-        <v>1</v>
-      </c>
-      <c r="I13" s="32" t="s">
+      <c r="H13" s="15">
+        <v>1</v>
+      </c>
+      <c r="I13" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="J13" s="13">
+      <c r="J13" s="15">
         <v>2.2</v>
       </c>
-      <c r="K13" s="13">
+      <c r="K13" s="15">
         <v>2.2</v>
       </c>
-      <c r="L13" s="33">
+      <c r="L13" s="18">
         <v>2.2</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="2:12">
-      <c r="B14" s="10"/>
-      <c r="C14" s="16" t="s">
+      <c r="B14" s="12"/>
+      <c r="C14" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="D14" s="21" t="s">
         <v>173</v>
       </c>
-      <c r="E14" s="16" t="s">
+      <c r="E14" s="20" t="s">
         <v>174</v>
       </c>
-      <c r="F14" s="16" t="s">
+      <c r="F14" s="20" t="s">
         <v>174</v>
       </c>
-      <c r="G14" s="18" t="s">
+      <c r="G14" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="H14" s="16">
-        <v>1</v>
-      </c>
-      <c r="I14" s="34" t="s">
+      <c r="H14" s="20">
+        <v>1</v>
+      </c>
+      <c r="I14" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="J14" s="16">
+      <c r="J14" s="20">
         <v>7.1</v>
       </c>
-      <c r="K14" s="16">
+      <c r="K14" s="20">
         <v>7.1</v>
       </c>
-      <c r="L14" s="35">
+      <c r="L14" s="24">
         <v>7.1</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="2:12">
-      <c r="B15" s="10"/>
-      <c r="C15" s="13" t="s">
+      <c r="B15" s="12"/>
+      <c r="C15" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="E15" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="F15" s="13" t="s">
+      <c r="F15" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="G15" s="14" t="s">
+      <c r="G15" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="H15" s="13">
-        <v>1</v>
-      </c>
-      <c r="I15" s="32" t="s">
+      <c r="H15" s="15">
+        <v>1</v>
+      </c>
+      <c r="I15" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="J15" s="13">
+      <c r="J15" s="15">
         <v>1.1</v>
       </c>
-      <c r="K15" s="13">
+      <c r="K15" s="15">
         <v>1.1</v>
       </c>
-      <c r="L15" s="33">
+      <c r="L15" s="18">
         <v>1.1</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="2:12">
-      <c r="B16" s="10"/>
-      <c r="C16" s="16" t="s">
+      <c r="B16" s="12"/>
+      <c r="C16" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="D16" s="17" t="s">
+      <c r="D16" s="21" t="s">
         <v>177</v>
       </c>
-      <c r="E16" s="16" t="s">
+      <c r="E16" s="20" t="s">
         <v>178</v>
       </c>
-      <c r="F16" s="16" t="s">
+      <c r="F16" s="20" t="s">
         <v>178</v>
       </c>
-      <c r="G16" s="18" t="s">
+      <c r="G16" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="H16" s="16">
-        <v>1</v>
-      </c>
-      <c r="I16" s="34" t="s">
+      <c r="H16" s="20">
+        <v>1</v>
+      </c>
+      <c r="I16" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="J16" s="16">
+      <c r="J16" s="20">
         <v>0.94</v>
       </c>
-      <c r="K16" s="16">
+      <c r="K16" s="20">
         <v>0.94</v>
       </c>
-      <c r="L16" s="35">
+      <c r="L16" s="24">
         <v>0.94</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="2:12">
-      <c r="B17" s="19"/>
-      <c r="C17" s="20"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="22">
-        <f t="shared" ref="H17:K17" si="0">SUM(H5:H16)</f>
+      <c r="B17" s="25"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="26"/>
+      <c r="H17" s="27">
+        <f t="shared" ref="H17:L17" si="0">SUM(H5:H16)</f>
         <v>12</v>
       </c>
-      <c r="I17" s="22"/>
-      <c r="J17" s="36">
+      <c r="I17" s="27"/>
+      <c r="J17" s="27">
         <f>SUM(J5:J16)</f>
         <v>24.38</v>
       </c>
-      <c r="K17" s="22">
+      <c r="K17" s="27">
         <f t="shared" si="0"/>
         <v>24.38</v>
       </c>
-      <c r="L17" s="37">
-        <f>SUM(L5:L16)</f>
+      <c r="L17" s="28">
+        <f t="shared" si="0"/>
         <v>24.38</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" ht="30" customHeight="1" spans="2:12">
-      <c r="B18" s="23" t="s">
+      <c r="B18" s="29" t="s">
         <v>179</v>
       </c>
-      <c r="C18" s="24"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="25"/>
-      <c r="H18" s="25"/>
-      <c r="I18" s="25"/>
-      <c r="J18" s="38"/>
-      <c r="K18" s="38"/>
-      <c r="L18" s="39"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="30"/>
+      <c r="H18" s="30"/>
+      <c r="I18" s="30"/>
+      <c r="J18" s="30"/>
+      <c r="K18" s="30"/>
+      <c r="L18" s="31"/>
     </row>
     <row r="19" spans="2:12">
-      <c r="B19" s="26"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="27"/>
-      <c r="H19" s="27"/>
-      <c r="I19" s="27"/>
-      <c r="J19" s="27"/>
-      <c r="K19" s="27"/>
-      <c r="L19" s="27"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="33"/>
+      <c r="E19" s="33"/>
+      <c r="F19" s="33"/>
+      <c r="G19" s="33"/>
+      <c r="H19" s="33"/>
+      <c r="I19" s="33"/>
+      <c r="J19" s="33"/>
+      <c r="K19" s="33"/>
+      <c r="L19" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="5">
